--- a/PD_Guide_Database.xlsx
+++ b/PD_Guide_Database.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thinkpad" sheetId="1" r:id="Ra43d4c033bc742ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ideapad" sheetId="2" r:id="R5a7f0b76cc3f4097"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Desktop" sheetId="3" r:id="R47a2e99da9f74d8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiny" sheetId="4" r:id="R4d2696775c734cdd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIO" sheetId="5" r:id="R70ae929d8348482a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dropdown_Master" sheetId="6" r:id="R1cef45db31f14771"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Related_Guide_Master" sheetId="7" r:id="R91638a911eaa4faf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="8" r:id="R196fb00d872f489f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thinkpad" sheetId="1" r:id="R422c0be726f44a98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ideapad" sheetId="2" r:id="R8e0cc2ce6deb4790"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Desktop" sheetId="3" r:id="Re1fac88399a34a04"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiny" sheetId="4" r:id="R5be67f4995fd4814"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIO" sheetId="5" r:id="Ra997b40995634f73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dropdown_Master" sheetId="6" r:id="Rbd5314a376f941fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Related_Guide_Master" sheetId="7" r:id="R869787fc6f484d45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="8" r:id="R45defd8f86ec4e34"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -495,9 +495,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -53358,7 +53358,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B12" t="str">
-        <x:v>PD Guide Toolkit v5.2.2 FRU ordering and uppercase detail output release.</x:v>
+        <x:v>PD Guide Toolkit v5.2.3 diagnostics, reference sync, and regression coverage release.</x:v>
       </x:c>
     </x:row>
     <x:row r="13">

--- a/PD_Guide_Database.xlsx
+++ b/PD_Guide_Database.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thinkpad" sheetId="1" r:id="R422c0be726f44a98"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ideapad" sheetId="2" r:id="R8e0cc2ce6deb4790"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Desktop" sheetId="3" r:id="Re1fac88399a34a04"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiny" sheetId="4" r:id="R5be67f4995fd4814"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIO" sheetId="5" r:id="Ra997b40995634f73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dropdown_Master" sheetId="6" r:id="Rbd5314a376f941fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Related_Guide_Master" sheetId="7" r:id="R869787fc6f484d45"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="8" r:id="R45defd8f86ec4e34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thinkpad" sheetId="1" r:id="Rc86649240ea3413b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ideapad" sheetId="2" r:id="Rff0b88775b224a04"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Desktop" sheetId="3" r:id="Rd41639c258794603"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiny" sheetId="4" r:id="Red959d44cc934728"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIO" sheetId="5" r:id="R95eb5545c5774887"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dropdown_Master" sheetId="6" r:id="Rf0b328804beb4bd7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Related_Guide_Master" sheetId="7" r:id="Rbcfc468084c74767"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="8" r:id="Reea97064ec6c4ab9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -682,16 +682,16 @@
         <x:v>No Power</x:v>
       </x:c>
       <x:c r="C4" s="55" t="str">
-        <x:v>Swap Adapter</x:v>
+        <x:v>Emergency Reset</x:v>
       </x:c>
       <x:c r="D4" s="55" t="str">
         <x:v>DD002</x:v>
       </x:c>
       <x:c r="E4" s="56" t="str">
-        <x:v>ทดสอบสลับ Adapter ตัวอื่น</x:v>
+        <x:v>ทดสอบเคลียร์ไฟ (Emergency Reset) โดยถอดสายชาร์จออก และจิ้มรูที่ใต้ตัวเครื่องประมาณ 5-10 วินาที จากนั้นเปิดเครื่องใหม่</x:v>
       </x:c>
       <x:c r="F4" s="56" t="str">
-        <x:v>Test with another adapter.</x:v>
+        <x:v>Perform an Emergency Reset by disconnecting the adapter and pressing the emergency-reset hole on the bottom of the computer for approximately 5–10 seconds, then turn the computer on again.</x:v>
       </x:c>
       <x:c r="G4" s="52"/>
     </x:row>
@@ -703,16 +703,16 @@
         <x:v>No Power</x:v>
       </x:c>
       <x:c r="C5" s="55" t="str">
-        <x:v>Emergency Reset</x:v>
+        <x:v>Swap Other Type-C Port</x:v>
       </x:c>
       <x:c r="D5" s="55" t="str">
         <x:v>DD002</x:v>
       </x:c>
       <x:c r="E5" s="56" t="str">
-        <x:v>ทดสอบเคลียร์ไฟ (Emergency Reset) โดยถอดสายชาร์จออก และจิ้มรูที่ใต้ตัวเครื่องประมาณ 5-10 วินาที จากนั้นเปิดเครื่องใหม่</x:v>
+        <x:v>ทดสอบสลับช่อง Type-C ช่องอื่น</x:v>
       </x:c>
       <x:c r="F5" s="56" t="str">
-        <x:v>Perform an Emergency Reset by disconnecting the adapter and pressing the emergency-reset hole on the bottom of the computer for approximately 5–10 seconds, then turn the computer on again.</x:v>
+        <x:v>Test with another USB Type-C port.</x:v>
       </x:c>
       <x:c r="G5" s="52"/>
     </x:row>
@@ -724,16 +724,16 @@
         <x:v>No Power</x:v>
       </x:c>
       <x:c r="C6" s="55" t="str">
-        <x:v>Swap Other Type-C Port</x:v>
+        <x:v>Swap Adapter</x:v>
       </x:c>
       <x:c r="D6" s="55" t="str">
         <x:v>DD002</x:v>
       </x:c>
       <x:c r="E6" s="56" t="str">
-        <x:v>ทดสอบสลับช่อง Type-C ช่องอื่น</x:v>
+        <x:v>ทดสอบสลับ Adapter ตัวอื่น</x:v>
       </x:c>
       <x:c r="F6" s="56" t="str">
-        <x:v>Test with another USB Type-C port.</x:v>
+        <x:v>Test with another adapter.</x:v>
       </x:c>
       <x:c r="G6" s="52"/>
     </x:row>
@@ -53358,7 +53358,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B12" t="str">
-        <x:v>PD Guide Toolkit v5.2.3 diagnostics, reference sync, and regression coverage release.</x:v>
+        <x:v>PD Guide Toolkit v5.2.4 global navigation, Code/User Guide library, and Global Search release.</x:v>
       </x:c>
     </x:row>
     <x:row r="13">

--- a/PD_Guide_Database.xlsx
+++ b/PD_Guide_Database.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thinkpad" sheetId="1" r:id="R4bd95488e0ee4087"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ideapad" sheetId="2" r:id="R1b15482e5471472a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Desktop" sheetId="3" r:id="R1ccb663f9a84410b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiny" sheetId="4" r:id="R58bc218892bb4bd0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIO" sheetId="5" r:id="Rb841cd0570bf42c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dropdown_Master" sheetId="6" r:id="R0a758f2a3a7a403a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Related_Guide_Master" sheetId="7" r:id="Rfa59dbd6b8ae4e3c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="8" r:id="R28531bdeb6804e26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thinkpad" sheetId="1" r:id="R7ad7002a8c2746e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ideapad" sheetId="2" r:id="R8cb92cb41b214d09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Desktop" sheetId="3" r:id="R98123bd67f05479f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiny" sheetId="4" r:id="Rfc6ac2b78dcc4f54"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIO" sheetId="5" r:id="R63c3ceb63f70462f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dropdown_Master" sheetId="6" r:id="R3b06f5ae91ab49b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Related_Guide_Master" sheetId="7" r:id="R03174c3a0ef24f18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="8" r:id="R2996f55b21154667"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53010,7 +53010,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B12" t="str">
-        <x:v>PD Guide Toolkit v5.2.4 global navigation, Code/User Guide library, and Global Search release.</x:v>
+        <x:v>PD Guide Toolkit v5.2.5 adds Labor Mapping with independent Province/Postal Code search.</x:v>
       </x:c>
     </x:row>
     <x:row r="13">

--- a/PD_Guide_Database.xlsx
+++ b/PD_Guide_Database.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thinkpad" sheetId="1" r:id="R7ad7002a8c2746e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ideapad" sheetId="2" r:id="R8cb92cb41b214d09"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Desktop" sheetId="3" r:id="R98123bd67f05479f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiny" sheetId="4" r:id="Rfc6ac2b78dcc4f54"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIO" sheetId="5" r:id="R63c3ceb63f70462f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dropdown_Master" sheetId="6" r:id="R3b06f5ae91ab49b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Related_Guide_Master" sheetId="7" r:id="R03174c3a0ef24f18"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="8" r:id="R2996f55b21154667"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thinkpad" sheetId="1" r:id="Recf7296a22e148f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ideapad" sheetId="2" r:id="Rb6164e3b50dd4962"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Desktop" sheetId="3" r:id="Rcf6cfbb734e84b13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiny" sheetId="4" r:id="R26f516866cdf4b6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIO" sheetId="5" r:id="Rcb3a229c07534ae2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dropdown_Master" sheetId="6" r:id="Rb3913aaeb1a14e16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Related_Guide_Master" sheetId="7" r:id="R6d2031311c054898"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="8" r:id="R14bb7df323fd4ac9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -11546,806 +11546,806 @@
       <x:c r="G517" s="52"/>
     </x:row>
     <x:row r="518" ht="16.5" customHeight="1">
-      <x:c r="A518" s="57"/>
-      <x:c r="B518" s="57"/>
-      <x:c r="C518" s="61"/>
-      <x:c r="D518" s="55"/>
-      <x:c r="E518" s="56"/>
-      <x:c r="F518" s="52"/>
-      <x:c r="G518" s="52"/>
+      <x:c r="A518"/>
+      <x:c r="B518"/>
+      <x:c r="C518"/>
+      <x:c r="D518"/>
+      <x:c r="E518"/>
+      <x:c r="F518"/>
+      <x:c r="G518"/>
     </x:row>
     <x:row r="519" ht="16.5" customHeight="1">
-      <x:c r="A519" s="57"/>
-      <x:c r="B519" s="57"/>
-      <x:c r="C519" s="61"/>
-      <x:c r="D519" s="61"/>
-      <x:c r="E519" s="56"/>
-      <x:c r="F519" s="52"/>
-      <x:c r="G519" s="52"/>
+      <x:c r="A519"/>
+      <x:c r="B519"/>
+      <x:c r="C519"/>
+      <x:c r="D519"/>
+      <x:c r="E519"/>
+      <x:c r="F519"/>
+      <x:c r="G519"/>
     </x:row>
     <x:row r="520" ht="16.5" customHeight="1">
-      <x:c r="A520" s="57"/>
-      <x:c r="B520" s="57"/>
-      <x:c r="C520" s="61"/>
-      <x:c r="D520" s="61"/>
-      <x:c r="E520" s="56"/>
-      <x:c r="F520" s="52"/>
-      <x:c r="G520" s="52"/>
+      <x:c r="A520"/>
+      <x:c r="B520"/>
+      <x:c r="C520"/>
+      <x:c r="D520"/>
+      <x:c r="E520"/>
+      <x:c r="F520"/>
+      <x:c r="G520"/>
     </x:row>
     <x:row r="521" ht="16.5" customHeight="1">
-      <x:c r="A521" s="57"/>
-      <x:c r="B521" s="57"/>
-      <x:c r="C521" s="61"/>
-      <x:c r="D521" s="61"/>
-      <x:c r="E521" s="56"/>
-      <x:c r="F521" s="52"/>
-      <x:c r="G521" s="52"/>
+      <x:c r="A521"/>
+      <x:c r="B521"/>
+      <x:c r="C521"/>
+      <x:c r="D521"/>
+      <x:c r="E521"/>
+      <x:c r="F521"/>
+      <x:c r="G521"/>
     </x:row>
     <x:row r="522" ht="16.5" customHeight="1">
-      <x:c r="A522" s="57"/>
-      <x:c r="B522" s="57"/>
-      <x:c r="C522" s="61"/>
-      <x:c r="D522" s="61"/>
-      <x:c r="E522" s="56"/>
-      <x:c r="F522" s="52"/>
-      <x:c r="G522" s="52"/>
+      <x:c r="A522"/>
+      <x:c r="B522"/>
+      <x:c r="C522"/>
+      <x:c r="D522"/>
+      <x:c r="E522"/>
+      <x:c r="F522"/>
+      <x:c r="G522"/>
     </x:row>
     <x:row r="523" ht="16.5" customHeight="1">
-      <x:c r="A523" s="57"/>
-      <x:c r="B523" s="57"/>
-      <x:c r="C523" s="61"/>
-      <x:c r="D523" s="61"/>
-      <x:c r="E523" s="56"/>
-      <x:c r="F523" s="52"/>
-      <x:c r="G523" s="52"/>
+      <x:c r="A523"/>
+      <x:c r="B523"/>
+      <x:c r="C523"/>
+      <x:c r="D523"/>
+      <x:c r="E523"/>
+      <x:c r="F523"/>
+      <x:c r="G523"/>
     </x:row>
     <x:row r="524" ht="16.5" customHeight="1">
-      <x:c r="A524" s="57"/>
-      <x:c r="B524" s="57"/>
-      <x:c r="C524" s="61"/>
-      <x:c r="D524" s="55"/>
-      <x:c r="E524" s="56"/>
-      <x:c r="F524" s="52"/>
-      <x:c r="G524" s="52"/>
+      <x:c r="A524"/>
+      <x:c r="B524"/>
+      <x:c r="C524"/>
+      <x:c r="D524"/>
+      <x:c r="E524"/>
+      <x:c r="F524"/>
+      <x:c r="G524"/>
     </x:row>
     <x:row r="525">
-      <x:c r="A525" s="51"/>
-      <x:c r="B525" s="51"/>
-      <x:c r="C525" s="52"/>
-      <x:c r="D525" s="62"/>
-      <x:c r="E525" s="52"/>
-      <x:c r="F525" s="52"/>
-      <x:c r="G525" s="52"/>
+      <x:c r="A525"/>
+      <x:c r="B525"/>
+      <x:c r="C525"/>
+      <x:c r="D525"/>
+      <x:c r="E525"/>
+      <x:c r="F525"/>
+      <x:c r="G525"/>
     </x:row>
     <x:row r="526" ht="16.5" customHeight="1">
-      <x:c r="A526" s="57"/>
-      <x:c r="B526" s="57"/>
-      <x:c r="C526" s="61"/>
-      <x:c r="D526" s="61"/>
-      <x:c r="E526" s="56"/>
-      <x:c r="F526" s="52"/>
-      <x:c r="G526" s="52"/>
+      <x:c r="A526"/>
+      <x:c r="B526"/>
+      <x:c r="C526"/>
+      <x:c r="D526"/>
+      <x:c r="E526"/>
+      <x:c r="F526"/>
+      <x:c r="G526"/>
     </x:row>
     <x:row r="527" ht="16.5" customHeight="1">
-      <x:c r="A527" s="57"/>
-      <x:c r="B527" s="57"/>
-      <x:c r="C527" s="61"/>
-      <x:c r="D527" s="61"/>
-      <x:c r="E527" s="56"/>
-      <x:c r="F527" s="52"/>
-      <x:c r="G527" s="52"/>
+      <x:c r="A527"/>
+      <x:c r="B527"/>
+      <x:c r="C527"/>
+      <x:c r="D527"/>
+      <x:c r="E527"/>
+      <x:c r="F527"/>
+      <x:c r="G527"/>
     </x:row>
     <x:row r="528" ht="16.5" customHeight="1">
-      <x:c r="A528" s="57"/>
-      <x:c r="B528" s="57"/>
-      <x:c r="C528" s="61"/>
-      <x:c r="D528" s="61"/>
-      <x:c r="E528" s="56"/>
-      <x:c r="F528" s="52"/>
-      <x:c r="G528" s="52"/>
+      <x:c r="A528"/>
+      <x:c r="B528"/>
+      <x:c r="C528"/>
+      <x:c r="D528"/>
+      <x:c r="E528"/>
+      <x:c r="F528"/>
+      <x:c r="G528"/>
     </x:row>
     <x:row r="529" ht="16.5" customHeight="1">
-      <x:c r="A529" s="57"/>
-      <x:c r="B529" s="57"/>
-      <x:c r="C529" s="61"/>
-      <x:c r="D529" s="61"/>
-      <x:c r="E529" s="56"/>
-      <x:c r="F529" s="52"/>
-      <x:c r="G529" s="52"/>
+      <x:c r="A529"/>
+      <x:c r="B529"/>
+      <x:c r="C529"/>
+      <x:c r="D529"/>
+      <x:c r="E529"/>
+      <x:c r="F529"/>
+      <x:c r="G529"/>
     </x:row>
     <x:row r="530" ht="16.5" customHeight="1">
-      <x:c r="A530" s="57"/>
-      <x:c r="B530" s="57"/>
-      <x:c r="C530" s="61"/>
-      <x:c r="D530" s="61"/>
-      <x:c r="E530" s="56"/>
-      <x:c r="F530" s="52"/>
-      <x:c r="G530" s="52"/>
+      <x:c r="A530"/>
+      <x:c r="B530"/>
+      <x:c r="C530"/>
+      <x:c r="D530"/>
+      <x:c r="E530"/>
+      <x:c r="F530"/>
+      <x:c r="G530"/>
     </x:row>
     <x:row r="531" ht="16.5" customHeight="1">
-      <x:c r="A531" s="57"/>
-      <x:c r="B531" s="57"/>
-      <x:c r="C531" s="61"/>
-      <x:c r="D531" s="55"/>
-      <x:c r="E531" s="56"/>
-      <x:c r="F531" s="52"/>
-      <x:c r="G531" s="52"/>
+      <x:c r="A531"/>
+      <x:c r="B531"/>
+      <x:c r="C531"/>
+      <x:c r="D531"/>
+      <x:c r="E531"/>
+      <x:c r="F531"/>
+      <x:c r="G531"/>
     </x:row>
     <x:row r="532" ht="16.5" customHeight="1">
-      <x:c r="A532" s="57"/>
-      <x:c r="B532" s="57"/>
-      <x:c r="C532" s="52"/>
-      <x:c r="D532" s="62"/>
-      <x:c r="E532" s="52"/>
-      <x:c r="F532" s="52"/>
-      <x:c r="G532" s="52"/>
+      <x:c r="A532"/>
+      <x:c r="B532"/>
+      <x:c r="C532"/>
+      <x:c r="D532"/>
+      <x:c r="E532"/>
+      <x:c r="F532"/>
+      <x:c r="G532"/>
     </x:row>
     <x:row r="533" ht="16.5" customHeight="1">
-      <x:c r="A533" s="57"/>
-      <x:c r="B533" s="57"/>
-      <x:c r="C533" s="61"/>
-      <x:c r="D533" s="61"/>
-      <x:c r="E533" s="56"/>
-      <x:c r="F533" s="52"/>
-      <x:c r="G533" s="52"/>
+      <x:c r="A533"/>
+      <x:c r="B533"/>
+      <x:c r="C533"/>
+      <x:c r="D533"/>
+      <x:c r="E533"/>
+      <x:c r="F533"/>
+      <x:c r="G533"/>
     </x:row>
     <x:row r="534" ht="16.5" customHeight="1">
-      <x:c r="A534" s="57"/>
-      <x:c r="B534" s="57"/>
-      <x:c r="C534" s="61"/>
-      <x:c r="D534" s="61"/>
-      <x:c r="E534" s="56"/>
-      <x:c r="F534" s="52"/>
-      <x:c r="G534" s="52"/>
+      <x:c r="A534"/>
+      <x:c r="B534"/>
+      <x:c r="C534"/>
+      <x:c r="D534"/>
+      <x:c r="E534"/>
+      <x:c r="F534"/>
+      <x:c r="G534"/>
     </x:row>
     <x:row r="535" ht="16.5" customHeight="1">
-      <x:c r="A535" s="57"/>
-      <x:c r="B535" s="57"/>
-      <x:c r="C535" s="61"/>
-      <x:c r="D535" s="61"/>
-      <x:c r="E535" s="56"/>
-      <x:c r="F535" s="52"/>
-      <x:c r="G535" s="52"/>
+      <x:c r="A535"/>
+      <x:c r="B535"/>
+      <x:c r="C535"/>
+      <x:c r="D535"/>
+      <x:c r="E535"/>
+      <x:c r="F535"/>
+      <x:c r="G535"/>
     </x:row>
     <x:row r="536" ht="16.5" customHeight="1">
-      <x:c r="A536" s="57"/>
-      <x:c r="B536" s="57"/>
-      <x:c r="C536" s="61"/>
-      <x:c r="D536" s="61"/>
-      <x:c r="E536" s="56"/>
-      <x:c r="F536" s="52"/>
-      <x:c r="G536" s="52"/>
+      <x:c r="A536"/>
+      <x:c r="B536"/>
+      <x:c r="C536"/>
+      <x:c r="D536"/>
+      <x:c r="E536"/>
+      <x:c r="F536"/>
+      <x:c r="G536"/>
     </x:row>
     <x:row r="537" ht="16.5" customHeight="1">
-      <x:c r="A537" s="57"/>
-      <x:c r="B537" s="57"/>
-      <x:c r="C537" s="61"/>
-      <x:c r="D537" s="55"/>
-      <x:c r="E537" s="56"/>
-      <x:c r="F537" s="52"/>
-      <x:c r="G537" s="52"/>
+      <x:c r="A537"/>
+      <x:c r="B537"/>
+      <x:c r="C537"/>
+      <x:c r="D537"/>
+      <x:c r="E537"/>
+      <x:c r="F537"/>
+      <x:c r="G537"/>
     </x:row>
     <x:row r="538" ht="16.5" customHeight="1">
-      <x:c r="A538" s="57"/>
-      <x:c r="B538" s="57"/>
-      <x:c r="C538" s="52"/>
-      <x:c r="D538" s="62"/>
-      <x:c r="E538" s="52"/>
-      <x:c r="F538" s="52"/>
-      <x:c r="G538" s="52"/>
+      <x:c r="A538"/>
+      <x:c r="B538"/>
+      <x:c r="C538"/>
+      <x:c r="D538"/>
+      <x:c r="E538"/>
+      <x:c r="F538"/>
+      <x:c r="G538"/>
     </x:row>
     <x:row r="539" ht="16.5" customHeight="1">
-      <x:c r="A539" s="57"/>
-      <x:c r="B539" s="57"/>
-      <x:c r="C539" s="61"/>
-      <x:c r="D539" s="61"/>
-      <x:c r="E539" s="56"/>
-      <x:c r="F539" s="52"/>
-      <x:c r="G539" s="52"/>
+      <x:c r="A539"/>
+      <x:c r="B539"/>
+      <x:c r="C539"/>
+      <x:c r="D539"/>
+      <x:c r="E539"/>
+      <x:c r="F539"/>
+      <x:c r="G539"/>
     </x:row>
     <x:row r="540" ht="16.5" customHeight="1">
-      <x:c r="A540" s="57"/>
-      <x:c r="B540" s="57"/>
-      <x:c r="C540" s="61"/>
-      <x:c r="D540" s="61"/>
-      <x:c r="E540" s="56"/>
-      <x:c r="F540" s="52"/>
-      <x:c r="G540" s="52"/>
+      <x:c r="A540"/>
+      <x:c r="B540"/>
+      <x:c r="C540"/>
+      <x:c r="D540"/>
+      <x:c r="E540"/>
+      <x:c r="F540"/>
+      <x:c r="G540"/>
     </x:row>
     <x:row r="541" ht="16.5" customHeight="1">
-      <x:c r="A541" s="57"/>
-      <x:c r="B541" s="57"/>
-      <x:c r="C541" s="61"/>
-      <x:c r="D541" s="61"/>
-      <x:c r="E541" s="56"/>
-      <x:c r="F541" s="52"/>
-      <x:c r="G541" s="52"/>
+      <x:c r="A541"/>
+      <x:c r="B541"/>
+      <x:c r="C541"/>
+      <x:c r="D541"/>
+      <x:c r="E541"/>
+      <x:c r="F541"/>
+      <x:c r="G541"/>
     </x:row>
     <x:row r="542" ht="16.5" customHeight="1">
-      <x:c r="A542" s="57"/>
-      <x:c r="B542" s="57"/>
-      <x:c r="C542" s="61"/>
-      <x:c r="D542" s="61"/>
-      <x:c r="E542" s="56"/>
-      <x:c r="F542" s="52"/>
-      <x:c r="G542" s="52"/>
+      <x:c r="A542"/>
+      <x:c r="B542"/>
+      <x:c r="C542"/>
+      <x:c r="D542"/>
+      <x:c r="E542"/>
+      <x:c r="F542"/>
+      <x:c r="G542"/>
     </x:row>
     <x:row r="543" ht="16.5" customHeight="1">
-      <x:c r="A543" s="57"/>
-      <x:c r="B543" s="57"/>
-      <x:c r="C543" s="61"/>
-      <x:c r="D543" s="61"/>
-      <x:c r="E543" s="56"/>
-      <x:c r="F543" s="52"/>
-      <x:c r="G543" s="52"/>
+      <x:c r="A543"/>
+      <x:c r="B543"/>
+      <x:c r="C543"/>
+      <x:c r="D543"/>
+      <x:c r="E543"/>
+      <x:c r="F543"/>
+      <x:c r="G543"/>
     </x:row>
     <x:row r="544" ht="16.5" customHeight="1">
-      <x:c r="A544" s="57"/>
-      <x:c r="B544" s="57"/>
-      <x:c r="C544" s="61"/>
-      <x:c r="D544" s="55"/>
-      <x:c r="E544" s="56"/>
-      <x:c r="F544" s="52"/>
-      <x:c r="G544" s="52"/>
+      <x:c r="A544"/>
+      <x:c r="B544"/>
+      <x:c r="C544"/>
+      <x:c r="D544"/>
+      <x:c r="E544"/>
+      <x:c r="F544"/>
+      <x:c r="G544"/>
     </x:row>
     <x:row r="545" ht="16.5" customHeight="1">
-      <x:c r="A545" s="57"/>
-      <x:c r="B545" s="57"/>
-      <x:c r="C545" s="61"/>
-      <x:c r="D545" s="61"/>
-      <x:c r="E545" s="56"/>
-      <x:c r="F545" s="52"/>
-      <x:c r="G545" s="52"/>
+      <x:c r="A545"/>
+      <x:c r="B545"/>
+      <x:c r="C545"/>
+      <x:c r="D545"/>
+      <x:c r="E545"/>
+      <x:c r="F545"/>
+      <x:c r="G545"/>
     </x:row>
     <x:row r="546" ht="16.5" customHeight="1">
-      <x:c r="A546" s="57"/>
-      <x:c r="B546" s="57"/>
-      <x:c r="C546" s="61"/>
-      <x:c r="D546" s="61"/>
-      <x:c r="E546" s="56"/>
-      <x:c r="F546" s="52"/>
-      <x:c r="G546" s="52"/>
+      <x:c r="A546"/>
+      <x:c r="B546"/>
+      <x:c r="C546"/>
+      <x:c r="D546"/>
+      <x:c r="E546"/>
+      <x:c r="F546"/>
+      <x:c r="G546"/>
     </x:row>
     <x:row r="547" ht="16.5" customHeight="1">
-      <x:c r="A547" s="57"/>
-      <x:c r="B547" s="57"/>
-      <x:c r="C547" s="61"/>
-      <x:c r="D547" s="61"/>
-      <x:c r="E547" s="56"/>
-      <x:c r="F547" s="52"/>
-      <x:c r="G547" s="52"/>
+      <x:c r="A547"/>
+      <x:c r="B547"/>
+      <x:c r="C547"/>
+      <x:c r="D547"/>
+      <x:c r="E547"/>
+      <x:c r="F547"/>
+      <x:c r="G547"/>
     </x:row>
     <x:row r="548" ht="16.5" customHeight="1">
-      <x:c r="A548" s="57"/>
-      <x:c r="B548" s="57"/>
-      <x:c r="C548" s="61"/>
-      <x:c r="D548" s="61"/>
-      <x:c r="E548" s="56"/>
-      <x:c r="F548" s="52"/>
-      <x:c r="G548" s="52"/>
+      <x:c r="A548"/>
+      <x:c r="B548"/>
+      <x:c r="C548"/>
+      <x:c r="D548"/>
+      <x:c r="E548"/>
+      <x:c r="F548"/>
+      <x:c r="G548"/>
     </x:row>
     <x:row r="549" ht="16.5" customHeight="1">
-      <x:c r="A549" s="57"/>
-      <x:c r="B549" s="57"/>
-      <x:c r="C549" s="61"/>
-      <x:c r="D549" s="61"/>
-      <x:c r="E549" s="56"/>
-      <x:c r="F549" s="52"/>
-      <x:c r="G549" s="52"/>
+      <x:c r="A549"/>
+      <x:c r="B549"/>
+      <x:c r="C549"/>
+      <x:c r="D549"/>
+      <x:c r="E549"/>
+      <x:c r="F549"/>
+      <x:c r="G549"/>
     </x:row>
     <x:row r="550" ht="16.5" customHeight="1">
-      <x:c r="A550" s="57"/>
-      <x:c r="B550" s="57"/>
-      <x:c r="C550" s="61"/>
-      <x:c r="D550" s="61"/>
-      <x:c r="E550" s="56"/>
-      <x:c r="F550" s="52"/>
-      <x:c r="G550" s="52"/>
+      <x:c r="A550"/>
+      <x:c r="B550"/>
+      <x:c r="C550"/>
+      <x:c r="D550"/>
+      <x:c r="E550"/>
+      <x:c r="F550"/>
+      <x:c r="G550"/>
     </x:row>
     <x:row r="551" ht="16.5" customHeight="1">
-      <x:c r="A551" s="57"/>
-      <x:c r="B551" s="57"/>
-      <x:c r="C551" s="61"/>
-      <x:c r="D551" s="55"/>
-      <x:c r="E551" s="56"/>
-      <x:c r="F551" s="52"/>
-      <x:c r="G551" s="52"/>
+      <x:c r="A551"/>
+      <x:c r="B551"/>
+      <x:c r="C551"/>
+      <x:c r="D551"/>
+      <x:c r="E551"/>
+      <x:c r="F551"/>
+      <x:c r="G551"/>
     </x:row>
     <x:row r="552" ht="16.5" customHeight="1">
-      <x:c r="A552" s="57"/>
-      <x:c r="B552" s="57"/>
-      <x:c r="C552" s="61"/>
-      <x:c r="D552" s="61"/>
-      <x:c r="E552" s="56"/>
-      <x:c r="F552" s="52"/>
-      <x:c r="G552" s="52"/>
+      <x:c r="A552"/>
+      <x:c r="B552"/>
+      <x:c r="C552"/>
+      <x:c r="D552"/>
+      <x:c r="E552"/>
+      <x:c r="F552"/>
+      <x:c r="G552"/>
     </x:row>
     <x:row r="553" ht="16.5" customHeight="1">
-      <x:c r="A553" s="57"/>
-      <x:c r="B553" s="57"/>
-      <x:c r="C553" s="61"/>
-      <x:c r="D553" s="61"/>
-      <x:c r="E553" s="56"/>
-      <x:c r="F553" s="52"/>
-      <x:c r="G553" s="52"/>
+      <x:c r="A553"/>
+      <x:c r="B553"/>
+      <x:c r="C553"/>
+      <x:c r="D553"/>
+      <x:c r="E553"/>
+      <x:c r="F553"/>
+      <x:c r="G553"/>
     </x:row>
     <x:row r="554" ht="16.5" customHeight="1">
-      <x:c r="A554" s="57"/>
-      <x:c r="B554" s="57"/>
-      <x:c r="C554" s="61"/>
-      <x:c r="D554" s="61"/>
-      <x:c r="E554" s="56"/>
-      <x:c r="F554" s="52"/>
-      <x:c r="G554" s="52"/>
+      <x:c r="A554"/>
+      <x:c r="B554"/>
+      <x:c r="C554"/>
+      <x:c r="D554"/>
+      <x:c r="E554"/>
+      <x:c r="F554"/>
+      <x:c r="G554"/>
     </x:row>
     <x:row r="555" ht="16.5" customHeight="1">
-      <x:c r="A555" s="57"/>
-      <x:c r="B555" s="57"/>
-      <x:c r="C555" s="61"/>
-      <x:c r="D555" s="61"/>
-      <x:c r="E555" s="56"/>
-      <x:c r="F555" s="52"/>
-      <x:c r="G555" s="52"/>
+      <x:c r="A555"/>
+      <x:c r="B555"/>
+      <x:c r="C555"/>
+      <x:c r="D555"/>
+      <x:c r="E555"/>
+      <x:c r="F555"/>
+      <x:c r="G555"/>
     </x:row>
     <x:row r="556" ht="16.5" customHeight="1">
-      <x:c r="A556" s="57"/>
-      <x:c r="B556" s="57"/>
-      <x:c r="C556" s="61"/>
-      <x:c r="D556" s="61"/>
-      <x:c r="E556" s="56"/>
-      <x:c r="F556" s="52"/>
-      <x:c r="G556" s="52"/>
+      <x:c r="A556"/>
+      <x:c r="B556"/>
+      <x:c r="C556"/>
+      <x:c r="D556"/>
+      <x:c r="E556"/>
+      <x:c r="F556"/>
+      <x:c r="G556"/>
     </x:row>
     <x:row r="557" ht="16.5" customHeight="1">
-      <x:c r="A557" s="57"/>
-      <x:c r="B557" s="57"/>
-      <x:c r="C557" s="61"/>
-      <x:c r="D557" s="55"/>
-      <x:c r="E557" s="56"/>
-      <x:c r="F557" s="52"/>
-      <x:c r="G557" s="52"/>
+      <x:c r="A557"/>
+      <x:c r="B557"/>
+      <x:c r="C557"/>
+      <x:c r="D557"/>
+      <x:c r="E557"/>
+      <x:c r="F557"/>
+      <x:c r="G557"/>
     </x:row>
     <x:row r="558">
-      <x:c r="A558" s="51"/>
-      <x:c r="B558" s="51"/>
-      <x:c r="C558" s="52"/>
-      <x:c r="D558" s="62"/>
-      <x:c r="E558" s="52"/>
-      <x:c r="F558" s="52"/>
-      <x:c r="G558" s="52"/>
+      <x:c r="A558"/>
+      <x:c r="B558"/>
+      <x:c r="C558"/>
+      <x:c r="D558"/>
+      <x:c r="E558"/>
+      <x:c r="F558"/>
+      <x:c r="G558"/>
     </x:row>
     <x:row r="559" ht="16.5" customHeight="1">
-      <x:c r="A559" s="21"/>
-      <x:c r="B559" s="21"/>
-      <x:c r="C559" s="7"/>
-      <x:c r="D559" s="7"/>
-      <x:c r="E559" s="1"/>
+      <x:c r="A559"/>
+      <x:c r="B559"/>
+      <x:c r="C559"/>
+      <x:c r="D559"/>
+      <x:c r="E559"/>
     </x:row>
     <x:row r="560" ht="16.5" customHeight="1">
-      <x:c r="A560" s="21"/>
-      <x:c r="B560" s="21"/>
-      <x:c r="C560" s="4"/>
-      <x:c r="D560" s="4"/>
-      <x:c r="E560" s="1"/>
+      <x:c r="A560"/>
+      <x:c r="B560"/>
+      <x:c r="C560"/>
+      <x:c r="D560"/>
+      <x:c r="E560"/>
     </x:row>
     <x:row r="561" ht="16.5" customHeight="1">
-      <x:c r="A561" s="21"/>
-      <x:c r="B561" s="21"/>
-      <x:c r="C561" s="4"/>
-      <x:c r="D561" s="4"/>
-      <x:c r="E561" s="1"/>
+      <x:c r="A561"/>
+      <x:c r="B561"/>
+      <x:c r="C561"/>
+      <x:c r="D561"/>
+      <x:c r="E561"/>
     </x:row>
     <x:row r="562" ht="16.5" customHeight="1">
-      <x:c r="A562" s="21"/>
-      <x:c r="B562" s="21"/>
-      <x:c r="C562" s="4"/>
-      <x:c r="D562" s="4"/>
-      <x:c r="E562" s="1"/>
+      <x:c r="A562"/>
+      <x:c r="B562"/>
+      <x:c r="C562"/>
+      <x:c r="D562"/>
+      <x:c r="E562"/>
     </x:row>
     <x:row r="563" ht="16.5" customHeight="1">
-      <x:c r="A563" s="21"/>
-      <x:c r="B563" s="21"/>
-      <x:c r="C563" s="4"/>
-      <x:c r="D563" s="4"/>
-      <x:c r="E563" s="1"/>
+      <x:c r="A563"/>
+      <x:c r="B563"/>
+      <x:c r="C563"/>
+      <x:c r="D563"/>
+      <x:c r="E563"/>
     </x:row>
     <x:row r="564" ht="16.5" customHeight="1">
-      <x:c r="A564" s="21"/>
-      <x:c r="B564" s="21"/>
-      <x:c r="C564" s="4"/>
-      <x:c r="D564" s="4"/>
-      <x:c r="E564" s="1"/>
+      <x:c r="A564"/>
+      <x:c r="B564"/>
+      <x:c r="C564"/>
+      <x:c r="D564"/>
+      <x:c r="E564"/>
     </x:row>
     <x:row r="565" ht="16.5" customHeight="1">
-      <x:c r="A565" s="21"/>
-      <x:c r="B565" s="21"/>
-      <x:c r="C565" s="4"/>
-      <x:c r="D565" s="4"/>
-      <x:c r="E565" s="1"/>
+      <x:c r="A565"/>
+      <x:c r="B565"/>
+      <x:c r="C565"/>
+      <x:c r="D565"/>
+      <x:c r="E565"/>
     </x:row>
     <x:row r="566" ht="16.5" customHeight="1">
-      <x:c r="A566" s="21"/>
-      <x:c r="B566" s="21"/>
-      <x:c r="C566" s="4"/>
-      <x:c r="D566" s="7"/>
-      <x:c r="E566" s="1"/>
+      <x:c r="A566"/>
+      <x:c r="B566"/>
+      <x:c r="C566"/>
+      <x:c r="D566"/>
+      <x:c r="E566"/>
     </x:row>
     <x:row r="567" ht="16.5" customHeight="1">
-      <x:c r="A567" s="21"/>
-      <x:c r="B567" s="21"/>
-      <x:c r="C567" s="4"/>
-      <x:c r="D567" s="4"/>
-      <x:c r="E567" s="1"/>
+      <x:c r="A567"/>
+      <x:c r="B567"/>
+      <x:c r="C567"/>
+      <x:c r="D567"/>
+      <x:c r="E567"/>
     </x:row>
     <x:row r="568" ht="16.5" customHeight="1">
-      <x:c r="A568" s="21"/>
-      <x:c r="B568" s="21"/>
-      <x:c r="C568" s="4"/>
-      <x:c r="D568" s="4"/>
-      <x:c r="E568" s="1"/>
+      <x:c r="A568"/>
+      <x:c r="B568"/>
+      <x:c r="C568"/>
+      <x:c r="D568"/>
+      <x:c r="E568"/>
     </x:row>
     <x:row r="569" ht="16.5" customHeight="1">
-      <x:c r="A569" s="21"/>
-      <x:c r="B569" s="21"/>
-      <x:c r="C569" s="4"/>
-      <x:c r="D569" s="4"/>
-      <x:c r="E569" s="1"/>
+      <x:c r="A569"/>
+      <x:c r="B569"/>
+      <x:c r="C569"/>
+      <x:c r="D569"/>
+      <x:c r="E569"/>
     </x:row>
     <x:row r="570" ht="16.5" customHeight="1">
-      <x:c r="A570" s="21"/>
-      <x:c r="B570" s="21"/>
-      <x:c r="C570" s="4"/>
-      <x:c r="D570" s="4"/>
-      <x:c r="E570" s="1"/>
+      <x:c r="A570"/>
+      <x:c r="B570"/>
+      <x:c r="C570"/>
+      <x:c r="D570"/>
+      <x:c r="E570"/>
     </x:row>
     <x:row r="571" ht="16.5" customHeight="1">
-      <x:c r="A571" s="21"/>
-      <x:c r="B571" s="21"/>
-      <x:c r="C571" s="4"/>
-      <x:c r="D571" s="4"/>
-      <x:c r="E571" s="1"/>
+      <x:c r="A571"/>
+      <x:c r="B571"/>
+      <x:c r="C571"/>
+      <x:c r="D571"/>
+      <x:c r="E571"/>
     </x:row>
     <x:row r="572" ht="16.5" customHeight="1">
-      <x:c r="A572" s="21"/>
-      <x:c r="B572" s="21"/>
-      <x:c r="C572" s="4"/>
-      <x:c r="D572" s="4"/>
-      <x:c r="E572" s="1"/>
+      <x:c r="A572"/>
+      <x:c r="B572"/>
+      <x:c r="C572"/>
+      <x:c r="D572"/>
+      <x:c r="E572"/>
     </x:row>
     <x:row r="573" ht="16.5" customHeight="1">
-      <x:c r="A573" s="21"/>
-      <x:c r="B573" s="21"/>
-      <x:c r="C573" s="4"/>
-      <x:c r="D573" s="4"/>
-      <x:c r="E573" s="1"/>
+      <x:c r="A573"/>
+      <x:c r="B573"/>
+      <x:c r="C573"/>
+      <x:c r="D573"/>
+      <x:c r="E573"/>
     </x:row>
     <x:row r="574" ht="16.5" customHeight="1">
-      <x:c r="A574" s="21"/>
-      <x:c r="B574" s="21"/>
-      <x:c r="C574" s="4"/>
-      <x:c r="D574" s="7"/>
-      <x:c r="E574" s="1"/>
+      <x:c r="A574"/>
+      <x:c r="B574"/>
+      <x:c r="C574"/>
+      <x:c r="D574"/>
+      <x:c r="E574"/>
     </x:row>
     <x:row r="575" ht="16.5" customHeight="1">
-      <x:c r="A575" s="21"/>
-      <x:c r="B575" s="21"/>
-      <x:c r="C575" s="4"/>
-      <x:c r="D575" s="4"/>
-      <x:c r="E575" s="1"/>
+      <x:c r="A575"/>
+      <x:c r="B575"/>
+      <x:c r="C575"/>
+      <x:c r="D575"/>
+      <x:c r="E575"/>
     </x:row>
     <x:row r="576" ht="16.5" customHeight="1">
-      <x:c r="A576" s="21"/>
-      <x:c r="B576" s="21"/>
-      <x:c r="C576" s="4"/>
-      <x:c r="D576" s="4"/>
-      <x:c r="E576" s="1"/>
+      <x:c r="A576"/>
+      <x:c r="B576"/>
+      <x:c r="C576"/>
+      <x:c r="D576"/>
+      <x:c r="E576"/>
     </x:row>
     <x:row r="577" ht="16.5" customHeight="1">
-      <x:c r="A577" s="21"/>
-      <x:c r="B577" s="21"/>
-      <x:c r="C577" s="4"/>
-      <x:c r="D577" s="4"/>
-      <x:c r="E577" s="1"/>
+      <x:c r="A577"/>
+      <x:c r="B577"/>
+      <x:c r="C577"/>
+      <x:c r="D577"/>
+      <x:c r="E577"/>
     </x:row>
     <x:row r="578" ht="16.5" customHeight="1">
-      <x:c r="A578" s="21"/>
-      <x:c r="B578" s="21"/>
-      <x:c r="C578" s="4"/>
-      <x:c r="D578" s="4"/>
-      <x:c r="E578" s="1"/>
+      <x:c r="A578"/>
+      <x:c r="B578"/>
+      <x:c r="C578"/>
+      <x:c r="D578"/>
+      <x:c r="E578"/>
     </x:row>
     <x:row r="579" ht="16.5" customHeight="1">
-      <x:c r="A579" s="21"/>
-      <x:c r="B579" s="21"/>
-      <x:c r="C579" s="4"/>
-      <x:c r="D579" s="4"/>
-      <x:c r="E579" s="1"/>
+      <x:c r="A579"/>
+      <x:c r="B579"/>
+      <x:c r="C579"/>
+      <x:c r="D579"/>
+      <x:c r="E579"/>
     </x:row>
     <x:row r="580" ht="16.5" customHeight="1">
-      <x:c r="A580" s="21"/>
-      <x:c r="B580" s="21"/>
-      <x:c r="C580" s="4"/>
-      <x:c r="D580" s="4"/>
-      <x:c r="E580" s="1"/>
+      <x:c r="A580"/>
+      <x:c r="B580"/>
+      <x:c r="C580"/>
+      <x:c r="D580"/>
+      <x:c r="E580"/>
     </x:row>
     <x:row r="581" ht="16.5" customHeight="1">
-      <x:c r="A581" s="21"/>
-      <x:c r="B581" s="21"/>
-      <x:c r="C581" s="4"/>
-      <x:c r="D581" s="4"/>
-      <x:c r="E581" s="1"/>
+      <x:c r="A581"/>
+      <x:c r="B581"/>
+      <x:c r="C581"/>
+      <x:c r="D581"/>
+      <x:c r="E581"/>
     </x:row>
     <x:row r="582" ht="16.5" customHeight="1">
-      <x:c r="A582" s="21"/>
-      <x:c r="B582" s="21"/>
-      <x:c r="C582" s="4"/>
-      <x:c r="D582" s="7"/>
-      <x:c r="E582" s="1"/>
+      <x:c r="A582"/>
+      <x:c r="B582"/>
+      <x:c r="C582"/>
+      <x:c r="D582"/>
+      <x:c r="E582"/>
     </x:row>
     <x:row r="583" ht="16.5" customHeight="1">
-      <x:c r="A583" s="21"/>
-      <x:c r="B583" s="21"/>
-      <x:c r="C583" s="4"/>
-      <x:c r="D583" s="4"/>
-      <x:c r="E583" s="1"/>
+      <x:c r="A583"/>
+      <x:c r="B583"/>
+      <x:c r="C583"/>
+      <x:c r="D583"/>
+      <x:c r="E583"/>
     </x:row>
     <x:row r="584" ht="16.5" customHeight="1">
-      <x:c r="A584" s="21"/>
-      <x:c r="B584" s="21"/>
-      <x:c r="C584" s="4"/>
-      <x:c r="D584" s="4"/>
-      <x:c r="E584" s="1"/>
+      <x:c r="A584"/>
+      <x:c r="B584"/>
+      <x:c r="C584"/>
+      <x:c r="D584"/>
+      <x:c r="E584"/>
     </x:row>
     <x:row r="585" ht="16.5" customHeight="1">
-      <x:c r="A585" s="21"/>
-      <x:c r="B585" s="21"/>
-      <x:c r="C585" s="4"/>
-      <x:c r="D585" s="4"/>
-      <x:c r="E585" s="1"/>
+      <x:c r="A585"/>
+      <x:c r="B585"/>
+      <x:c r="C585"/>
+      <x:c r="D585"/>
+      <x:c r="E585"/>
     </x:row>
     <x:row r="586" ht="16.5" customHeight="1">
-      <x:c r="A586" s="21"/>
-      <x:c r="B586" s="21"/>
-      <x:c r="C586" s="4"/>
-      <x:c r="D586" s="4"/>
-      <x:c r="E586" s="1"/>
+      <x:c r="A586"/>
+      <x:c r="B586"/>
+      <x:c r="C586"/>
+      <x:c r="D586"/>
+      <x:c r="E586"/>
     </x:row>
     <x:row r="587" ht="16.5" customHeight="1">
-      <x:c r="A587" s="21"/>
-      <x:c r="B587" s="21"/>
-      <x:c r="C587" s="4"/>
-      <x:c r="D587" s="4"/>
-      <x:c r="E587" s="1"/>
+      <x:c r="A587"/>
+      <x:c r="B587"/>
+      <x:c r="C587"/>
+      <x:c r="D587"/>
+      <x:c r="E587"/>
     </x:row>
     <x:row r="588" ht="16.5" customHeight="1">
-      <x:c r="A588" s="21"/>
-      <x:c r="B588" s="21"/>
-      <x:c r="C588" s="4"/>
-      <x:c r="D588" s="4"/>
-      <x:c r="E588" s="1"/>
+      <x:c r="A588"/>
+      <x:c r="B588"/>
+      <x:c r="C588"/>
+      <x:c r="D588"/>
+      <x:c r="E588"/>
     </x:row>
     <x:row r="589" ht="16.5" customHeight="1">
-      <x:c r="A589" s="21"/>
-      <x:c r="B589" s="21"/>
-      <x:c r="C589" s="4"/>
-      <x:c r="D589" s="4"/>
-      <x:c r="E589" s="1"/>
+      <x:c r="A589"/>
+      <x:c r="B589"/>
+      <x:c r="C589"/>
+      <x:c r="D589"/>
+      <x:c r="E589"/>
     </x:row>
     <x:row r="590" ht="16.5" customHeight="1">
-      <x:c r="A590" s="21"/>
-      <x:c r="B590" s="21"/>
-      <x:c r="C590" s="4"/>
-      <x:c r="D590" s="7"/>
-      <x:c r="E590" s="1"/>
+      <x:c r="A590"/>
+      <x:c r="B590"/>
+      <x:c r="C590"/>
+      <x:c r="D590"/>
+      <x:c r="E590"/>
     </x:row>
     <x:row r="591" ht="16.5" customHeight="1">
-      <x:c r="A591" s="21"/>
-      <x:c r="B591" s="21"/>
+      <x:c r="A591"/>
+      <x:c r="B591"/>
       <x:c r="C591"/>
-      <x:c r="D591" s="9"/>
+      <x:c r="D591"/>
     </x:row>
     <x:row r="592" ht="16.5" customHeight="1">
-      <x:c r="A592" s="21"/>
-      <x:c r="B592" s="21"/>
-      <x:c r="C592" s="4"/>
-      <x:c r="D592" s="9"/>
-      <x:c r="E592" s="1"/>
+      <x:c r="A592"/>
+      <x:c r="B592"/>
+      <x:c r="C592"/>
+      <x:c r="D592"/>
+      <x:c r="E592"/>
     </x:row>
     <x:row r="593" ht="16.5" customHeight="1">
-      <x:c r="A593" s="21"/>
-      <x:c r="B593" s="21"/>
-      <x:c r="C593" s="4"/>
-      <x:c r="D593" s="4"/>
-      <x:c r="E593" s="1"/>
+      <x:c r="A593"/>
+      <x:c r="B593"/>
+      <x:c r="C593"/>
+      <x:c r="D593"/>
+      <x:c r="E593"/>
     </x:row>
     <x:row r="594" ht="16.5" customHeight="1">
-      <x:c r="A594" s="21"/>
-      <x:c r="B594" s="21"/>
-      <x:c r="C594" s="4"/>
-      <x:c r="D594" s="4"/>
-      <x:c r="E594" s="1"/>
+      <x:c r="A594"/>
+      <x:c r="B594"/>
+      <x:c r="C594"/>
+      <x:c r="D594"/>
+      <x:c r="E594"/>
     </x:row>
     <x:row r="595" ht="16.5" customHeight="1">
-      <x:c r="A595" s="21"/>
-      <x:c r="B595" s="21"/>
-      <x:c r="C595" s="4"/>
-      <x:c r="D595" s="4"/>
-      <x:c r="E595" s="1"/>
+      <x:c r="A595"/>
+      <x:c r="B595"/>
+      <x:c r="C595"/>
+      <x:c r="D595"/>
+      <x:c r="E595"/>
     </x:row>
     <x:row r="596" ht="16.5" customHeight="1">
-      <x:c r="A596" s="21"/>
-      <x:c r="B596" s="21"/>
-      <x:c r="C596" s="4"/>
-      <x:c r="D596" s="4"/>
-      <x:c r="E596" s="1"/>
+      <x:c r="A596"/>
+      <x:c r="B596"/>
+      <x:c r="C596"/>
+      <x:c r="D596"/>
+      <x:c r="E596"/>
     </x:row>
     <x:row r="597" ht="16.5" customHeight="1">
-      <x:c r="A597" s="21"/>
-      <x:c r="B597" s="21"/>
-      <x:c r="C597" s="4"/>
-      <x:c r="D597" s="4"/>
-      <x:c r="E597" s="1"/>
+      <x:c r="A597"/>
+      <x:c r="B597"/>
+      <x:c r="C597"/>
+      <x:c r="D597"/>
+      <x:c r="E597"/>
     </x:row>
     <x:row r="598" ht="16.5" customHeight="1">
-      <x:c r="A598" s="21"/>
-      <x:c r="B598" s="21"/>
-      <x:c r="C598" s="4"/>
-      <x:c r="D598" s="4"/>
-      <x:c r="E598" s="1"/>
+      <x:c r="A598"/>
+      <x:c r="B598"/>
+      <x:c r="C598"/>
+      <x:c r="D598"/>
+      <x:c r="E598"/>
     </x:row>
     <x:row r="599" ht="16.5" customHeight="1">
-      <x:c r="A599" s="21"/>
-      <x:c r="B599" s="21"/>
-      <x:c r="C599" s="4"/>
-      <x:c r="D599" s="7"/>
-      <x:c r="E599" s="1"/>
+      <x:c r="A599"/>
+      <x:c r="B599"/>
+      <x:c r="C599"/>
+      <x:c r="D599"/>
+      <x:c r="E599"/>
     </x:row>
     <x:row r="600" ht="16.5" customHeight="1">
-      <x:c r="A600" s="21"/>
-      <x:c r="B600" s="21"/>
-      <x:c r="C600" s="4"/>
-      <x:c r="D600" s="4"/>
-      <x:c r="E600" s="1"/>
+      <x:c r="A600"/>
+      <x:c r="B600"/>
+      <x:c r="C600"/>
+      <x:c r="D600"/>
+      <x:c r="E600"/>
     </x:row>
     <x:row r="601" ht="16.5" customHeight="1">
-      <x:c r="A601" s="21"/>
-      <x:c r="B601" s="21"/>
-      <x:c r="C601" s="4"/>
-      <x:c r="D601" s="4"/>
-      <x:c r="E601" s="1"/>
+      <x:c r="A601"/>
+      <x:c r="B601"/>
+      <x:c r="C601"/>
+      <x:c r="D601"/>
+      <x:c r="E601"/>
     </x:row>
     <x:row r="602" ht="16.5" customHeight="1">
-      <x:c r="A602" s="21"/>
-      <x:c r="B602" s="21"/>
-      <x:c r="C602" s="4"/>
-      <x:c r="D602" s="4"/>
-      <x:c r="E602" s="1"/>
+      <x:c r="A602"/>
+      <x:c r="B602"/>
+      <x:c r="C602"/>
+      <x:c r="D602"/>
+      <x:c r="E602"/>
     </x:row>
     <x:row r="603" ht="16.5" customHeight="1">
-      <x:c r="A603" s="21"/>
-      <x:c r="B603" s="21"/>
-      <x:c r="C603" s="4"/>
-      <x:c r="D603" s="4"/>
-      <x:c r="E603" s="1"/>
+      <x:c r="A603"/>
+      <x:c r="B603"/>
+      <x:c r="C603"/>
+      <x:c r="D603"/>
+      <x:c r="E603"/>
     </x:row>
     <x:row r="604" ht="16.5" customHeight="1">
-      <x:c r="A604" s="21"/>
-      <x:c r="B604" s="21"/>
-      <x:c r="C604" s="4"/>
-      <x:c r="D604" s="4"/>
-      <x:c r="E604" s="1"/>
+      <x:c r="A604"/>
+      <x:c r="B604"/>
+      <x:c r="C604"/>
+      <x:c r="D604"/>
+      <x:c r="E604"/>
     </x:row>
     <x:row r="605" ht="16.5" customHeight="1">
-      <x:c r="A605" s="21"/>
-      <x:c r="B605" s="21"/>
-      <x:c r="C605" s="4"/>
-      <x:c r="D605" s="4"/>
-      <x:c r="E605" s="1"/>
+      <x:c r="A605"/>
+      <x:c r="B605"/>
+      <x:c r="C605"/>
+      <x:c r="D605"/>
+      <x:c r="E605"/>
     </x:row>
     <x:row r="606" ht="16.5" customHeight="1">
-      <x:c r="A606" s="21"/>
-      <x:c r="B606" s="21"/>
-      <x:c r="C606" s="4"/>
-      <x:c r="D606" s="4"/>
-      <x:c r="E606" s="1"/>
+      <x:c r="A606"/>
+      <x:c r="B606"/>
+      <x:c r="C606"/>
+      <x:c r="D606"/>
+      <x:c r="E606"/>
     </x:row>
     <x:row r="607" ht="16.5" customHeight="1">
-      <x:c r="A607" s="21"/>
-      <x:c r="B607" s="21"/>
-      <x:c r="C607" s="4"/>
-      <x:c r="D607" s="4"/>
-      <x:c r="E607" s="1"/>
+      <x:c r="A607"/>
+      <x:c r="B607"/>
+      <x:c r="C607"/>
+      <x:c r="D607"/>
+      <x:c r="E607"/>
     </x:row>
     <x:row r="608" ht="16.5" customHeight="1">
-      <x:c r="A608" s="21"/>
-      <x:c r="B608" s="21"/>
-      <x:c r="C608" s="4"/>
-      <x:c r="D608" s="4"/>
-      <x:c r="E608" s="1"/>
+      <x:c r="A608"/>
+      <x:c r="B608"/>
+      <x:c r="C608"/>
+      <x:c r="D608"/>
+      <x:c r="E608"/>
     </x:row>
     <x:row r="609" ht="16.5" customHeight="1">
-      <x:c r="A609" s="21"/>
-      <x:c r="B609" s="21"/>
-      <x:c r="C609" s="4"/>
-      <x:c r="D609" s="4"/>
-      <x:c r="E609" s="1"/>
+      <x:c r="A609"/>
+      <x:c r="B609"/>
+      <x:c r="C609"/>
+      <x:c r="D609"/>
+      <x:c r="E609"/>
     </x:row>
     <x:row r="610" ht="16.5" customHeight="1">
-      <x:c r="A610" s="21"/>
-      <x:c r="B610" s="21"/>
-      <x:c r="C610" s="4"/>
-      <x:c r="D610" s="7"/>
-      <x:c r="E610" s="1"/>
+      <x:c r="A610"/>
+      <x:c r="B610"/>
+      <x:c r="C610"/>
+      <x:c r="D610"/>
+      <x:c r="E610"/>
     </x:row>
     <x:row r="611" ht="16.5" customHeight="1">
-      <x:c r="A611" s="21"/>
-      <x:c r="B611" s="21"/>
-      <x:c r="C611" s="4"/>
-      <x:c r="D611" s="4"/>
-      <x:c r="E611" s="1"/>
+      <x:c r="A611"/>
+      <x:c r="B611"/>
+      <x:c r="C611"/>
+      <x:c r="D611"/>
+      <x:c r="E611"/>
     </x:row>
     <x:row r="612" ht="16.5" customHeight="1">
-      <x:c r="A612" s="21"/>
-      <x:c r="B612" s="21"/>
-      <x:c r="C612" s="4"/>
-      <x:c r="D612" s="4"/>
-      <x:c r="E612" s="1"/>
+      <x:c r="A612"/>
+      <x:c r="B612"/>
+      <x:c r="C612"/>
+      <x:c r="D612"/>
+      <x:c r="E612"/>
     </x:row>
     <x:row r="613" ht="16.5" customHeight="1">
-      <x:c r="A613" s="21"/>
-      <x:c r="B613" s="21"/>
-      <x:c r="C613" s="4"/>
-      <x:c r="D613" s="4"/>
-      <x:c r="E613" s="1"/>
+      <x:c r="A613"/>
+      <x:c r="B613"/>
+      <x:c r="C613"/>
+      <x:c r="D613"/>
+      <x:c r="E613"/>
     </x:row>
     <x:row r="614" ht="16.5" customHeight="1">
-      <x:c r="A614" s="21"/>
-      <x:c r="B614" s="21"/>
-      <x:c r="C614" s="4"/>
-      <x:c r="D614" s="4"/>
-      <x:c r="E614" s="1"/>
+      <x:c r="A614"/>
+      <x:c r="B614"/>
+      <x:c r="C614"/>
+      <x:c r="D614"/>
+      <x:c r="E614"/>
     </x:row>
     <x:row r="615" ht="16.5" customHeight="1">
-      <x:c r="A615" s="21"/>
-      <x:c r="B615" s="21"/>
-      <x:c r="C615" s="4"/>
-      <x:c r="D615" s="4"/>
-      <x:c r="E615" s="1"/>
+      <x:c r="A615"/>
+      <x:c r="B615"/>
+      <x:c r="C615"/>
+      <x:c r="D615"/>
+      <x:c r="E615"/>
     </x:row>
     <x:row r="616" ht="16.5" customHeight="1">
-      <x:c r="A616" s="21"/>
-      <x:c r="B616" s="21"/>
-      <x:c r="C616" s="4"/>
-      <x:c r="D616" s="4"/>
-      <x:c r="E616" s="1"/>
+      <x:c r="A616"/>
+      <x:c r="B616"/>
+      <x:c r="C616"/>
+      <x:c r="D616"/>
+      <x:c r="E616"/>
     </x:row>
     <x:row r="617" ht="16.5" customHeight="1">
-      <x:c r="A617" s="21"/>
-      <x:c r="B617" s="21"/>
-      <x:c r="C617" s="4"/>
-      <x:c r="D617" s="4"/>
-      <x:c r="E617" s="1"/>
+      <x:c r="A617"/>
+      <x:c r="B617"/>
+      <x:c r="C617"/>
+      <x:c r="D617"/>
+      <x:c r="E617"/>
     </x:row>
     <x:row r="618" ht="16.5" customHeight="1">
-      <x:c r="A618" s="21"/>
-      <x:c r="B618" s="21"/>
-      <x:c r="C618" s="4"/>
-      <x:c r="D618" s="4"/>
-      <x:c r="E618" s="1"/>
+      <x:c r="A618"/>
+      <x:c r="B618"/>
+      <x:c r="C618"/>
+      <x:c r="D618"/>
+      <x:c r="E618"/>
     </x:row>
     <x:row r="619" ht="16.5" customHeight="1">
-      <x:c r="A619" s="21"/>
-      <x:c r="B619" s="21"/>
-      <x:c r="C619" s="4"/>
-      <x:c r="D619" s="4"/>
-      <x:c r="E619" s="1"/>
+      <x:c r="A619"/>
+      <x:c r="B619"/>
+      <x:c r="C619"/>
+      <x:c r="D619"/>
+      <x:c r="E619"/>
     </x:row>
     <x:row r="620" ht="16.5" customHeight="1">
-      <x:c r="A620" s="19"/>
-      <x:c r="B620" s="19"/>
-      <x:c r="C620" s="4"/>
-      <x:c r="D620" s="7"/>
-      <x:c r="E620" s="1"/>
+      <x:c r="A620"/>
+      <x:c r="B620"/>
+      <x:c r="C620"/>
+      <x:c r="D620"/>
+      <x:c r="E620"/>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="21">
@@ -23085,386 +23085,386 @@
       <x:c r="G503" s="52"/>
     </x:row>
     <x:row r="504">
-      <x:c r="A504" s="51"/>
-      <x:c r="B504" s="51"/>
-      <x:c r="C504" s="52"/>
-      <x:c r="D504" s="52"/>
-      <x:c r="E504" s="52"/>
-      <x:c r="F504" s="52"/>
-      <x:c r="G504" s="52"/>
+      <x:c r="A504"/>
+      <x:c r="B504"/>
+      <x:c r="C504"/>
+      <x:c r="D504"/>
+      <x:c r="E504"/>
+      <x:c r="F504"/>
+      <x:c r="G504"/>
     </x:row>
     <x:row r="505">
-      <x:c r="A505" s="51"/>
-      <x:c r="B505" s="51"/>
-      <x:c r="C505" s="52"/>
-      <x:c r="D505" s="52"/>
-      <x:c r="E505" s="52"/>
-      <x:c r="F505" s="52"/>
-      <x:c r="G505" s="52"/>
+      <x:c r="A505"/>
+      <x:c r="B505"/>
+      <x:c r="C505"/>
+      <x:c r="D505"/>
+      <x:c r="E505"/>
+      <x:c r="F505"/>
+      <x:c r="G505"/>
     </x:row>
     <x:row r="506">
-      <x:c r="A506" s="51"/>
-      <x:c r="B506" s="51"/>
-      <x:c r="C506" s="52"/>
-      <x:c r="D506" s="52"/>
-      <x:c r="E506" s="52"/>
-      <x:c r="F506" s="52"/>
-      <x:c r="G506" s="52"/>
+      <x:c r="A506"/>
+      <x:c r="B506"/>
+      <x:c r="C506"/>
+      <x:c r="D506"/>
+      <x:c r="E506"/>
+      <x:c r="F506"/>
+      <x:c r="G506"/>
     </x:row>
     <x:row r="507">
-      <x:c r="A507" s="51"/>
-      <x:c r="B507" s="51"/>
-      <x:c r="C507" s="52"/>
-      <x:c r="D507" s="52"/>
-      <x:c r="E507" s="52"/>
-      <x:c r="F507" s="52"/>
-      <x:c r="G507" s="52"/>
+      <x:c r="A507"/>
+      <x:c r="B507"/>
+      <x:c r="C507"/>
+      <x:c r="D507"/>
+      <x:c r="E507"/>
+      <x:c r="F507"/>
+      <x:c r="G507"/>
     </x:row>
     <x:row r="508">
-      <x:c r="A508" s="51"/>
-      <x:c r="B508" s="51"/>
-      <x:c r="C508" s="52"/>
-      <x:c r="D508" s="52"/>
-      <x:c r="E508" s="52"/>
-      <x:c r="F508" s="52"/>
-      <x:c r="G508" s="52"/>
+      <x:c r="A508"/>
+      <x:c r="B508"/>
+      <x:c r="C508"/>
+      <x:c r="D508"/>
+      <x:c r="E508"/>
+      <x:c r="F508"/>
+      <x:c r="G508"/>
     </x:row>
     <x:row r="509">
-      <x:c r="A509" s="51"/>
-      <x:c r="B509" s="51"/>
-      <x:c r="C509" s="52"/>
-      <x:c r="D509" s="52"/>
-      <x:c r="E509" s="52"/>
-      <x:c r="F509" s="52"/>
-      <x:c r="G509" s="52"/>
+      <x:c r="A509"/>
+      <x:c r="B509"/>
+      <x:c r="C509"/>
+      <x:c r="D509"/>
+      <x:c r="E509"/>
+      <x:c r="F509"/>
+      <x:c r="G509"/>
     </x:row>
     <x:row r="510">
-      <x:c r="A510" s="51"/>
-      <x:c r="B510" s="51"/>
-      <x:c r="C510" s="52"/>
-      <x:c r="D510" s="52"/>
-      <x:c r="E510" s="52"/>
-      <x:c r="F510" s="52"/>
-      <x:c r="G510" s="52"/>
+      <x:c r="A510"/>
+      <x:c r="B510"/>
+      <x:c r="C510"/>
+      <x:c r="D510"/>
+      <x:c r="E510"/>
+      <x:c r="F510"/>
+      <x:c r="G510"/>
     </x:row>
     <x:row r="511">
-      <x:c r="A511" s="51"/>
-      <x:c r="B511" s="51"/>
-      <x:c r="C511" s="52"/>
-      <x:c r="D511" s="52"/>
-      <x:c r="E511" s="52"/>
-      <x:c r="F511" s="52"/>
-      <x:c r="G511" s="52"/>
+      <x:c r="A511"/>
+      <x:c r="B511"/>
+      <x:c r="C511"/>
+      <x:c r="D511"/>
+      <x:c r="E511"/>
+      <x:c r="F511"/>
+      <x:c r="G511"/>
     </x:row>
     <x:row r="512">
-      <x:c r="A512" s="51"/>
-      <x:c r="B512" s="51"/>
-      <x:c r="C512" s="52"/>
-      <x:c r="D512" s="52"/>
-      <x:c r="E512" s="52"/>
-      <x:c r="F512" s="52"/>
-      <x:c r="G512" s="52"/>
+      <x:c r="A512"/>
+      <x:c r="B512"/>
+      <x:c r="C512"/>
+      <x:c r="D512"/>
+      <x:c r="E512"/>
+      <x:c r="F512"/>
+      <x:c r="G512"/>
     </x:row>
     <x:row r="513">
-      <x:c r="A513" s="51"/>
-      <x:c r="B513" s="51"/>
-      <x:c r="C513" s="52"/>
-      <x:c r="D513" s="52"/>
-      <x:c r="E513" s="52"/>
-      <x:c r="F513" s="52"/>
-      <x:c r="G513" s="52"/>
+      <x:c r="A513"/>
+      <x:c r="B513"/>
+      <x:c r="C513"/>
+      <x:c r="D513"/>
+      <x:c r="E513"/>
+      <x:c r="F513"/>
+      <x:c r="G513"/>
     </x:row>
     <x:row r="514">
-      <x:c r="A514" s="51"/>
-      <x:c r="B514" s="51"/>
-      <x:c r="C514" s="52"/>
-      <x:c r="D514" s="52"/>
-      <x:c r="E514" s="52"/>
-      <x:c r="F514" s="52"/>
-      <x:c r="G514" s="52"/>
+      <x:c r="A514"/>
+      <x:c r="B514"/>
+      <x:c r="C514"/>
+      <x:c r="D514"/>
+      <x:c r="E514"/>
+      <x:c r="F514"/>
+      <x:c r="G514"/>
     </x:row>
     <x:row r="515">
-      <x:c r="A515" s="51"/>
-      <x:c r="B515" s="51"/>
-      <x:c r="C515" s="52"/>
-      <x:c r="D515" s="52"/>
-      <x:c r="E515" s="52"/>
-      <x:c r="F515" s="52"/>
-      <x:c r="G515" s="52"/>
+      <x:c r="A515"/>
+      <x:c r="B515"/>
+      <x:c r="C515"/>
+      <x:c r="D515"/>
+      <x:c r="E515"/>
+      <x:c r="F515"/>
+      <x:c r="G515"/>
     </x:row>
     <x:row r="516">
-      <x:c r="A516" s="51"/>
-      <x:c r="B516" s="51"/>
-      <x:c r="C516" s="52"/>
-      <x:c r="D516" s="52"/>
-      <x:c r="E516" s="52"/>
-      <x:c r="F516" s="52"/>
-      <x:c r="G516" s="52"/>
+      <x:c r="A516"/>
+      <x:c r="B516"/>
+      <x:c r="C516"/>
+      <x:c r="D516"/>
+      <x:c r="E516"/>
+      <x:c r="F516"/>
+      <x:c r="G516"/>
     </x:row>
     <x:row r="517">
-      <x:c r="A517" s="51"/>
-      <x:c r="B517" s="51"/>
-      <x:c r="C517" s="52"/>
-      <x:c r="D517" s="52"/>
-      <x:c r="E517" s="52"/>
-      <x:c r="F517" s="52"/>
-      <x:c r="G517" s="52"/>
+      <x:c r="A517"/>
+      <x:c r="B517"/>
+      <x:c r="C517"/>
+      <x:c r="D517"/>
+      <x:c r="E517"/>
+      <x:c r="F517"/>
+      <x:c r="G517"/>
     </x:row>
     <x:row r="518">
-      <x:c r="A518" s="51"/>
-      <x:c r="B518" s="51"/>
-      <x:c r="C518" s="52"/>
-      <x:c r="D518" s="52"/>
-      <x:c r="E518" s="52"/>
-      <x:c r="F518" s="52"/>
-      <x:c r="G518" s="52"/>
+      <x:c r="A518"/>
+      <x:c r="B518"/>
+      <x:c r="C518"/>
+      <x:c r="D518"/>
+      <x:c r="E518"/>
+      <x:c r="F518"/>
+      <x:c r="G518"/>
     </x:row>
     <x:row r="519">
-      <x:c r="A519" s="51"/>
-      <x:c r="B519" s="51"/>
-      <x:c r="C519" s="52"/>
-      <x:c r="D519" s="52"/>
-      <x:c r="E519" s="52"/>
-      <x:c r="F519" s="52"/>
-      <x:c r="G519" s="52"/>
+      <x:c r="A519"/>
+      <x:c r="B519"/>
+      <x:c r="C519"/>
+      <x:c r="D519"/>
+      <x:c r="E519"/>
+      <x:c r="F519"/>
+      <x:c r="G519"/>
     </x:row>
     <x:row r="520">
-      <x:c r="A520" s="51"/>
-      <x:c r="B520" s="51"/>
-      <x:c r="C520" s="52"/>
-      <x:c r="D520" s="52"/>
-      <x:c r="E520" s="52"/>
-      <x:c r="F520" s="52"/>
-      <x:c r="G520" s="52"/>
+      <x:c r="A520"/>
+      <x:c r="B520"/>
+      <x:c r="C520"/>
+      <x:c r="D520"/>
+      <x:c r="E520"/>
+      <x:c r="F520"/>
+      <x:c r="G520"/>
     </x:row>
     <x:row r="521">
-      <x:c r="A521" s="51"/>
-      <x:c r="B521" s="51"/>
-      <x:c r="C521" s="52"/>
-      <x:c r="D521" s="52"/>
-      <x:c r="E521" s="52"/>
-      <x:c r="F521" s="52"/>
-      <x:c r="G521" s="52"/>
+      <x:c r="A521"/>
+      <x:c r="B521"/>
+      <x:c r="C521"/>
+      <x:c r="D521"/>
+      <x:c r="E521"/>
+      <x:c r="F521"/>
+      <x:c r="G521"/>
     </x:row>
     <x:row r="522">
-      <x:c r="A522" s="51"/>
-      <x:c r="B522" s="51"/>
-      <x:c r="C522" s="52"/>
-      <x:c r="D522" s="52"/>
-      <x:c r="E522" s="52"/>
-      <x:c r="F522" s="52"/>
-      <x:c r="G522" s="52"/>
+      <x:c r="A522"/>
+      <x:c r="B522"/>
+      <x:c r="C522"/>
+      <x:c r="D522"/>
+      <x:c r="E522"/>
+      <x:c r="F522"/>
+      <x:c r="G522"/>
     </x:row>
     <x:row r="523">
-      <x:c r="A523" s="51"/>
-      <x:c r="B523" s="51"/>
-      <x:c r="C523" s="52"/>
-      <x:c r="D523" s="52"/>
-      <x:c r="E523" s="52"/>
-      <x:c r="F523" s="52"/>
-      <x:c r="G523" s="52"/>
+      <x:c r="A523"/>
+      <x:c r="B523"/>
+      <x:c r="C523"/>
+      <x:c r="D523"/>
+      <x:c r="E523"/>
+      <x:c r="F523"/>
+      <x:c r="G523"/>
     </x:row>
     <x:row r="524">
-      <x:c r="A524" s="51"/>
-      <x:c r="B524" s="51"/>
-      <x:c r="C524" s="52"/>
-      <x:c r="D524" s="52"/>
-      <x:c r="E524" s="52"/>
-      <x:c r="F524" s="52"/>
-      <x:c r="G524" s="52"/>
+      <x:c r="A524"/>
+      <x:c r="B524"/>
+      <x:c r="C524"/>
+      <x:c r="D524"/>
+      <x:c r="E524"/>
+      <x:c r="F524"/>
+      <x:c r="G524"/>
     </x:row>
     <x:row r="525">
-      <x:c r="A525" s="51"/>
-      <x:c r="B525" s="51"/>
-      <x:c r="C525" s="52"/>
-      <x:c r="D525" s="52"/>
-      <x:c r="E525" s="52"/>
-      <x:c r="F525" s="52"/>
-      <x:c r="G525" s="52"/>
+      <x:c r="A525"/>
+      <x:c r="B525"/>
+      <x:c r="C525"/>
+      <x:c r="D525"/>
+      <x:c r="E525"/>
+      <x:c r="F525"/>
+      <x:c r="G525"/>
     </x:row>
     <x:row r="526">
-      <x:c r="A526" s="51"/>
-      <x:c r="B526" s="51"/>
-      <x:c r="C526" s="52"/>
-      <x:c r="D526" s="52"/>
-      <x:c r="E526" s="52"/>
-      <x:c r="F526" s="52"/>
-      <x:c r="G526" s="52"/>
+      <x:c r="A526"/>
+      <x:c r="B526"/>
+      <x:c r="C526"/>
+      <x:c r="D526"/>
+      <x:c r="E526"/>
+      <x:c r="F526"/>
+      <x:c r="G526"/>
     </x:row>
     <x:row r="527">
-      <x:c r="A527" s="51"/>
-      <x:c r="B527" s="51"/>
-      <x:c r="C527" s="52"/>
-      <x:c r="D527" s="52"/>
-      <x:c r="E527" s="52"/>
-      <x:c r="F527" s="52"/>
-      <x:c r="G527" s="52"/>
+      <x:c r="A527"/>
+      <x:c r="B527"/>
+      <x:c r="C527"/>
+      <x:c r="D527"/>
+      <x:c r="E527"/>
+      <x:c r="F527"/>
+      <x:c r="G527"/>
     </x:row>
     <x:row r="528">
-      <x:c r="A528" s="51"/>
-      <x:c r="B528" s="51"/>
-      <x:c r="C528" s="52"/>
-      <x:c r="D528" s="52"/>
-      <x:c r="E528" s="52"/>
-      <x:c r="F528" s="52"/>
-      <x:c r="G528" s="52"/>
+      <x:c r="A528"/>
+      <x:c r="B528"/>
+      <x:c r="C528"/>
+      <x:c r="D528"/>
+      <x:c r="E528"/>
+      <x:c r="F528"/>
+      <x:c r="G528"/>
     </x:row>
     <x:row r="529">
-      <x:c r="A529" s="51"/>
-      <x:c r="B529" s="51"/>
-      <x:c r="C529" s="52"/>
-      <x:c r="D529" s="52"/>
-      <x:c r="E529" s="52"/>
-      <x:c r="F529" s="52"/>
-      <x:c r="G529" s="52"/>
+      <x:c r="A529"/>
+      <x:c r="B529"/>
+      <x:c r="C529"/>
+      <x:c r="D529"/>
+      <x:c r="E529"/>
+      <x:c r="F529"/>
+      <x:c r="G529"/>
     </x:row>
     <x:row r="530">
-      <x:c r="A530" s="51"/>
-      <x:c r="B530" s="51"/>
-      <x:c r="C530" s="52"/>
-      <x:c r="D530" s="52"/>
-      <x:c r="E530" s="52"/>
-      <x:c r="F530" s="52"/>
-      <x:c r="G530" s="52"/>
+      <x:c r="A530"/>
+      <x:c r="B530"/>
+      <x:c r="C530"/>
+      <x:c r="D530"/>
+      <x:c r="E530"/>
+      <x:c r="F530"/>
+      <x:c r="G530"/>
     </x:row>
     <x:row r="531">
-      <x:c r="A531" s="51"/>
-      <x:c r="B531" s="51"/>
-      <x:c r="C531" s="52"/>
-      <x:c r="D531" s="52"/>
-      <x:c r="E531" s="52"/>
-      <x:c r="F531" s="52"/>
-      <x:c r="G531" s="52"/>
+      <x:c r="A531"/>
+      <x:c r="B531"/>
+      <x:c r="C531"/>
+      <x:c r="D531"/>
+      <x:c r="E531"/>
+      <x:c r="F531"/>
+      <x:c r="G531"/>
     </x:row>
     <x:row r="532">
-      <x:c r="A532" s="51"/>
-      <x:c r="B532" s="51"/>
-      <x:c r="C532" s="52"/>
-      <x:c r="D532" s="52"/>
-      <x:c r="E532" s="52"/>
-      <x:c r="F532" s="52"/>
-      <x:c r="G532" s="52"/>
+      <x:c r="A532"/>
+      <x:c r="B532"/>
+      <x:c r="C532"/>
+      <x:c r="D532"/>
+      <x:c r="E532"/>
+      <x:c r="F532"/>
+      <x:c r="G532"/>
     </x:row>
     <x:row r="533">
-      <x:c r="A533" s="51"/>
-      <x:c r="B533" s="51"/>
-      <x:c r="C533" s="52"/>
-      <x:c r="D533" s="52"/>
-      <x:c r="E533" s="52"/>
-      <x:c r="F533" s="52"/>
-      <x:c r="G533" s="52"/>
+      <x:c r="A533"/>
+      <x:c r="B533"/>
+      <x:c r="C533"/>
+      <x:c r="D533"/>
+      <x:c r="E533"/>
+      <x:c r="F533"/>
+      <x:c r="G533"/>
     </x:row>
     <x:row r="534">
-      <x:c r="A534" s="51"/>
-      <x:c r="B534" s="51"/>
-      <x:c r="C534" s="52"/>
-      <x:c r="D534" s="52"/>
-      <x:c r="E534" s="52"/>
-      <x:c r="F534" s="52"/>
-      <x:c r="G534" s="52"/>
+      <x:c r="A534"/>
+      <x:c r="B534"/>
+      <x:c r="C534"/>
+      <x:c r="D534"/>
+      <x:c r="E534"/>
+      <x:c r="F534"/>
+      <x:c r="G534"/>
     </x:row>
     <x:row r="535">
-      <x:c r="A535" s="51"/>
-      <x:c r="B535" s="51"/>
-      <x:c r="C535" s="52"/>
-      <x:c r="D535" s="52"/>
-      <x:c r="E535" s="52"/>
-      <x:c r="F535" s="52"/>
-      <x:c r="G535" s="52"/>
+      <x:c r="A535"/>
+      <x:c r="B535"/>
+      <x:c r="C535"/>
+      <x:c r="D535"/>
+      <x:c r="E535"/>
+      <x:c r="F535"/>
+      <x:c r="G535"/>
     </x:row>
     <x:row r="536">
-      <x:c r="A536" s="51"/>
-      <x:c r="B536" s="51"/>
-      <x:c r="C536" s="52"/>
-      <x:c r="D536" s="52"/>
-      <x:c r="E536" s="52"/>
-      <x:c r="F536" s="52"/>
-      <x:c r="G536" s="52"/>
+      <x:c r="A536"/>
+      <x:c r="B536"/>
+      <x:c r="C536"/>
+      <x:c r="D536"/>
+      <x:c r="E536"/>
+      <x:c r="F536"/>
+      <x:c r="G536"/>
     </x:row>
     <x:row r="537">
-      <x:c r="A537" s="51"/>
-      <x:c r="B537" s="51"/>
-      <x:c r="C537" s="52"/>
-      <x:c r="D537" s="52"/>
-      <x:c r="E537" s="52"/>
-      <x:c r="F537" s="52"/>
-      <x:c r="G537" s="52"/>
+      <x:c r="A537"/>
+      <x:c r="B537"/>
+      <x:c r="C537"/>
+      <x:c r="D537"/>
+      <x:c r="E537"/>
+      <x:c r="F537"/>
+      <x:c r="G537"/>
     </x:row>
     <x:row r="538">
-      <x:c r="A538" s="51"/>
-      <x:c r="B538" s="51"/>
-      <x:c r="C538" s="52"/>
-      <x:c r="D538" s="52"/>
-      <x:c r="E538" s="52"/>
-      <x:c r="F538" s="52"/>
-      <x:c r="G538" s="52"/>
+      <x:c r="A538"/>
+      <x:c r="B538"/>
+      <x:c r="C538"/>
+      <x:c r="D538"/>
+      <x:c r="E538"/>
+      <x:c r="F538"/>
+      <x:c r="G538"/>
     </x:row>
     <x:row r="539">
-      <x:c r="A539" s="51"/>
-      <x:c r="B539" s="51"/>
-      <x:c r="C539" s="52"/>
-      <x:c r="D539" s="52"/>
-      <x:c r="E539" s="52"/>
-      <x:c r="F539" s="52"/>
-      <x:c r="G539" s="52"/>
+      <x:c r="A539"/>
+      <x:c r="B539"/>
+      <x:c r="C539"/>
+      <x:c r="D539"/>
+      <x:c r="E539"/>
+      <x:c r="F539"/>
+      <x:c r="G539"/>
     </x:row>
     <x:row r="540">
-      <x:c r="A540" s="51"/>
-      <x:c r="B540" s="51"/>
-      <x:c r="C540" s="52"/>
-      <x:c r="D540" s="52"/>
-      <x:c r="E540" s="52"/>
-      <x:c r="F540" s="52"/>
-      <x:c r="G540" s="52"/>
+      <x:c r="A540"/>
+      <x:c r="B540"/>
+      <x:c r="C540"/>
+      <x:c r="D540"/>
+      <x:c r="E540"/>
+      <x:c r="F540"/>
+      <x:c r="G540"/>
     </x:row>
     <x:row r="541">
-      <x:c r="A541" s="51"/>
-      <x:c r="B541" s="51"/>
-      <x:c r="C541" s="52"/>
-      <x:c r="D541" s="52"/>
-      <x:c r="E541" s="52"/>
-      <x:c r="F541" s="52"/>
-      <x:c r="G541" s="52"/>
+      <x:c r="A541"/>
+      <x:c r="B541"/>
+      <x:c r="C541"/>
+      <x:c r="D541"/>
+      <x:c r="E541"/>
+      <x:c r="F541"/>
+      <x:c r="G541"/>
     </x:row>
     <x:row r="542">
-      <x:c r="A542" s="51"/>
-      <x:c r="B542" s="51"/>
-      <x:c r="C542" s="52"/>
-      <x:c r="D542" s="52"/>
-      <x:c r="E542" s="52"/>
-      <x:c r="F542" s="52"/>
-      <x:c r="G542" s="52"/>
+      <x:c r="A542"/>
+      <x:c r="B542"/>
+      <x:c r="C542"/>
+      <x:c r="D542"/>
+      <x:c r="E542"/>
+      <x:c r="F542"/>
+      <x:c r="G542"/>
     </x:row>
     <x:row r="543">
-      <x:c r="A543" s="51"/>
-      <x:c r="B543" s="51"/>
-      <x:c r="C543" s="52"/>
-      <x:c r="D543" s="52"/>
-      <x:c r="E543" s="52"/>
-      <x:c r="F543" s="52"/>
-      <x:c r="G543" s="52"/>
+      <x:c r="A543"/>
+      <x:c r="B543"/>
+      <x:c r="C543"/>
+      <x:c r="D543"/>
+      <x:c r="E543"/>
+      <x:c r="F543"/>
+      <x:c r="G543"/>
     </x:row>
     <x:row r="544">
-      <x:c r="A544" s="51"/>
-      <x:c r="B544" s="51"/>
-      <x:c r="C544" s="52"/>
-      <x:c r="D544" s="52"/>
-      <x:c r="E544" s="52"/>
-      <x:c r="F544" s="52"/>
-      <x:c r="G544" s="52"/>
+      <x:c r="A544"/>
+      <x:c r="B544"/>
+      <x:c r="C544"/>
+      <x:c r="D544"/>
+      <x:c r="E544"/>
+      <x:c r="F544"/>
+      <x:c r="G544"/>
     </x:row>
     <x:row r="545">
-      <x:c r="A545" s="51"/>
-      <x:c r="B545" s="51"/>
-      <x:c r="C545" s="52"/>
-      <x:c r="D545" s="52"/>
-      <x:c r="E545" s="52"/>
-      <x:c r="F545" s="52"/>
-      <x:c r="G545" s="52"/>
+      <x:c r="A545"/>
+      <x:c r="B545"/>
+      <x:c r="C545"/>
+      <x:c r="D545"/>
+      <x:c r="E545"/>
+      <x:c r="F545"/>
+      <x:c r="G545"/>
     </x:row>
     <x:row r="546">
-      <x:c r="A546" s="23"/>
-      <x:c r="B546" s="23"/>
+      <x:c r="A546"/>
+      <x:c r="B546"/>
       <x:c r="C546"/>
       <x:c r="D546"/>
       <x:c r="E546"/>
@@ -23472,8 +23472,8 @@
       <x:c r="G546"/>
     </x:row>
     <x:row r="547">
-      <x:c r="A547" s="23"/>
-      <x:c r="B547" s="23"/>
+      <x:c r="A547"/>
+      <x:c r="B547"/>
       <x:c r="C547"/>
       <x:c r="D547"/>
       <x:c r="E547"/>
@@ -23481,8 +23481,8 @@
       <x:c r="G547"/>
     </x:row>
     <x:row r="548">
-      <x:c r="A548" s="23"/>
-      <x:c r="B548" s="23"/>
+      <x:c r="A548"/>
+      <x:c r="B548"/>
       <x:c r="C548"/>
       <x:c r="D548"/>
       <x:c r="E548"/>
@@ -23490,8 +23490,8 @@
       <x:c r="G548"/>
     </x:row>
     <x:row r="549">
-      <x:c r="A549" s="23"/>
-      <x:c r="B549" s="23"/>
+      <x:c r="A549"/>
+      <x:c r="B549"/>
       <x:c r="C549"/>
       <x:c r="D549"/>
       <x:c r="E549"/>
@@ -23499,8 +23499,8 @@
       <x:c r="G549"/>
     </x:row>
     <x:row r="550">
-      <x:c r="A550" s="23"/>
-      <x:c r="B550" s="23"/>
+      <x:c r="A550"/>
+      <x:c r="B550"/>
       <x:c r="C550"/>
       <x:c r="D550"/>
       <x:c r="E550"/>
@@ -23508,8 +23508,8 @@
       <x:c r="G550"/>
     </x:row>
     <x:row r="551">
-      <x:c r="A551" s="23"/>
-      <x:c r="B551" s="23"/>
+      <x:c r="A551"/>
+      <x:c r="B551"/>
       <x:c r="C551"/>
       <x:c r="D551"/>
       <x:c r="E551"/>
@@ -23517,8 +23517,8 @@
       <x:c r="G551"/>
     </x:row>
     <x:row r="552">
-      <x:c r="A552" s="23"/>
-      <x:c r="B552" s="23"/>
+      <x:c r="A552"/>
+      <x:c r="B552"/>
       <x:c r="C552"/>
       <x:c r="D552"/>
       <x:c r="E552"/>
@@ -23526,8 +23526,8 @@
       <x:c r="G552"/>
     </x:row>
     <x:row r="553">
-      <x:c r="A553" s="23"/>
-      <x:c r="B553" s="23"/>
+      <x:c r="A553"/>
+      <x:c r="B553"/>
       <x:c r="C553"/>
       <x:c r="D553"/>
       <x:c r="E553"/>
@@ -23535,8 +23535,8 @@
       <x:c r="G553"/>
     </x:row>
     <x:row r="554">
-      <x:c r="A554" s="23"/>
-      <x:c r="B554" s="23"/>
+      <x:c r="A554"/>
+      <x:c r="B554"/>
       <x:c r="C554"/>
       <x:c r="D554"/>
       <x:c r="E554"/>
@@ -23544,8 +23544,8 @@
       <x:c r="G554"/>
     </x:row>
     <x:row r="555">
-      <x:c r="A555" s="23"/>
-      <x:c r="B555" s="23"/>
+      <x:c r="A555"/>
+      <x:c r="B555"/>
       <x:c r="C555"/>
       <x:c r="D555"/>
       <x:c r="E555"/>
@@ -23553,8 +23553,8 @@
       <x:c r="G555"/>
     </x:row>
     <x:row r="556">
-      <x:c r="A556" s="23"/>
-      <x:c r="B556" s="23"/>
+      <x:c r="A556"/>
+      <x:c r="B556"/>
       <x:c r="C556"/>
       <x:c r="D556"/>
       <x:c r="E556"/>
@@ -23562,8 +23562,8 @@
       <x:c r="G556"/>
     </x:row>
     <x:row r="557">
-      <x:c r="A557" s="23"/>
-      <x:c r="B557" s="23"/>
+      <x:c r="A557"/>
+      <x:c r="B557"/>
       <x:c r="C557"/>
       <x:c r="D557"/>
       <x:c r="E557"/>
@@ -23571,8 +23571,8 @@
       <x:c r="G557"/>
     </x:row>
     <x:row r="558">
-      <x:c r="A558" s="23"/>
-      <x:c r="B558" s="23"/>
+      <x:c r="A558"/>
+      <x:c r="B558"/>
       <x:c r="C558"/>
       <x:c r="D558"/>
       <x:c r="E558"/>
@@ -23580,8 +23580,8 @@
       <x:c r="G558"/>
     </x:row>
     <x:row r="559">
-      <x:c r="A559" s="23"/>
-      <x:c r="B559" s="23"/>
+      <x:c r="A559"/>
+      <x:c r="B559"/>
       <x:c r="C559"/>
       <x:c r="D559"/>
       <x:c r="E559"/>
@@ -23589,8 +23589,8 @@
       <x:c r="G559"/>
     </x:row>
     <x:row r="560">
-      <x:c r="A560" s="23"/>
-      <x:c r="B560" s="23"/>
+      <x:c r="A560"/>
+      <x:c r="B560"/>
       <x:c r="C560"/>
       <x:c r="D560"/>
       <x:c r="E560"/>
@@ -23598,8 +23598,8 @@
       <x:c r="G560"/>
     </x:row>
     <x:row r="561">
-      <x:c r="A561" s="23"/>
-      <x:c r="B561" s="23"/>
+      <x:c r="A561"/>
+      <x:c r="B561"/>
       <x:c r="C561"/>
       <x:c r="D561"/>
       <x:c r="E561"/>
@@ -23607,8 +23607,8 @@
       <x:c r="G561"/>
     </x:row>
     <x:row r="562">
-      <x:c r="A562" s="23"/>
-      <x:c r="B562" s="23"/>
+      <x:c r="A562"/>
+      <x:c r="B562"/>
       <x:c r="C562"/>
       <x:c r="D562"/>
       <x:c r="E562"/>
@@ -23616,8 +23616,8 @@
       <x:c r="G562"/>
     </x:row>
     <x:row r="563">
-      <x:c r="A563" s="23"/>
-      <x:c r="B563" s="23"/>
+      <x:c r="A563"/>
+      <x:c r="B563"/>
       <x:c r="C563"/>
       <x:c r="D563"/>
       <x:c r="E563"/>
@@ -23625,8 +23625,8 @@
       <x:c r="G563"/>
     </x:row>
     <x:row r="564">
-      <x:c r="A564" s="23"/>
-      <x:c r="B564" s="23"/>
+      <x:c r="A564"/>
+      <x:c r="B564"/>
       <x:c r="C564"/>
       <x:c r="D564"/>
       <x:c r="E564"/>
@@ -23634,8 +23634,8 @@
       <x:c r="G564"/>
     </x:row>
     <x:row r="565">
-      <x:c r="A565" s="23"/>
-      <x:c r="B565" s="23"/>
+      <x:c r="A565"/>
+      <x:c r="B565"/>
       <x:c r="C565"/>
       <x:c r="D565"/>
       <x:c r="E565"/>
@@ -23643,8 +23643,8 @@
       <x:c r="G565"/>
     </x:row>
     <x:row r="566">
-      <x:c r="A566" s="23"/>
-      <x:c r="B566" s="23"/>
+      <x:c r="A566"/>
+      <x:c r="B566"/>
       <x:c r="C566"/>
       <x:c r="D566"/>
       <x:c r="E566"/>
@@ -23652,8 +23652,8 @@
       <x:c r="G566"/>
     </x:row>
     <x:row r="567">
-      <x:c r="A567" s="23"/>
-      <x:c r="B567" s="23"/>
+      <x:c r="A567"/>
+      <x:c r="B567"/>
       <x:c r="C567"/>
       <x:c r="D567"/>
       <x:c r="E567"/>
@@ -23661,8 +23661,8 @@
       <x:c r="G567"/>
     </x:row>
     <x:row r="568">
-      <x:c r="A568" s="23"/>
-      <x:c r="B568" s="23"/>
+      <x:c r="A568"/>
+      <x:c r="B568"/>
       <x:c r="C568"/>
       <x:c r="D568"/>
       <x:c r="E568"/>
@@ -23670,8 +23670,8 @@
       <x:c r="G568"/>
     </x:row>
     <x:row r="569">
-      <x:c r="A569" s="23"/>
-      <x:c r="B569" s="23"/>
+      <x:c r="A569"/>
+      <x:c r="B569"/>
       <x:c r="C569"/>
       <x:c r="D569"/>
       <x:c r="E569"/>
@@ -23679,8 +23679,8 @@
       <x:c r="G569"/>
     </x:row>
     <x:row r="570">
-      <x:c r="A570" s="23"/>
-      <x:c r="B570" s="23"/>
+      <x:c r="A570"/>
+      <x:c r="B570"/>
       <x:c r="C570"/>
       <x:c r="D570"/>
       <x:c r="E570"/>
@@ -23688,8 +23688,8 @@
       <x:c r="G570"/>
     </x:row>
     <x:row r="571">
-      <x:c r="A571" s="23"/>
-      <x:c r="B571" s="23"/>
+      <x:c r="A571"/>
+      <x:c r="B571"/>
       <x:c r="C571"/>
       <x:c r="D571"/>
       <x:c r="E571"/>
@@ -23697,8 +23697,8 @@
       <x:c r="G571"/>
     </x:row>
     <x:row r="572">
-      <x:c r="A572" s="23"/>
-      <x:c r="B572" s="23"/>
+      <x:c r="A572"/>
+      <x:c r="B572"/>
       <x:c r="C572"/>
       <x:c r="D572"/>
       <x:c r="E572"/>
@@ -23706,8 +23706,8 @@
       <x:c r="G572"/>
     </x:row>
     <x:row r="573">
-      <x:c r="A573" s="23"/>
-      <x:c r="B573" s="23"/>
+      <x:c r="A573"/>
+      <x:c r="B573"/>
       <x:c r="C573"/>
       <x:c r="D573"/>
       <x:c r="E573"/>
@@ -23715,8 +23715,8 @@
       <x:c r="G573"/>
     </x:row>
     <x:row r="574">
-      <x:c r="A574" s="23"/>
-      <x:c r="B574" s="23"/>
+      <x:c r="A574"/>
+      <x:c r="B574"/>
       <x:c r="C574"/>
       <x:c r="D574"/>
       <x:c r="E574"/>
@@ -23724,8 +23724,8 @@
       <x:c r="G574"/>
     </x:row>
     <x:row r="575">
-      <x:c r="A575" s="23"/>
-      <x:c r="B575" s="23"/>
+      <x:c r="A575"/>
+      <x:c r="B575"/>
       <x:c r="C575"/>
       <x:c r="D575"/>
       <x:c r="E575"/>
@@ -23733,8 +23733,8 @@
       <x:c r="G575"/>
     </x:row>
     <x:row r="576">
-      <x:c r="A576" s="23"/>
-      <x:c r="B576" s="23"/>
+      <x:c r="A576"/>
+      <x:c r="B576"/>
       <x:c r="C576"/>
       <x:c r="D576"/>
       <x:c r="E576"/>
@@ -23742,8 +23742,8 @@
       <x:c r="G576"/>
     </x:row>
     <x:row r="577">
-      <x:c r="A577" s="23"/>
-      <x:c r="B577" s="23"/>
+      <x:c r="A577"/>
+      <x:c r="B577"/>
       <x:c r="C577"/>
       <x:c r="D577"/>
       <x:c r="E577"/>
@@ -23751,8 +23751,8 @@
       <x:c r="G577"/>
     </x:row>
     <x:row r="578">
-      <x:c r="A578" s="23"/>
-      <x:c r="B578" s="23"/>
+      <x:c r="A578"/>
+      <x:c r="B578"/>
       <x:c r="C578"/>
       <x:c r="D578"/>
       <x:c r="E578"/>
@@ -23760,8 +23760,8 @@
       <x:c r="G578"/>
     </x:row>
     <x:row r="579">
-      <x:c r="A579" s="23"/>
-      <x:c r="B579" s="23"/>
+      <x:c r="A579"/>
+      <x:c r="B579"/>
       <x:c r="C579"/>
       <x:c r="D579"/>
       <x:c r="E579"/>
@@ -23769,8 +23769,8 @@
       <x:c r="G579"/>
     </x:row>
     <x:row r="580">
-      <x:c r="A580" s="23"/>
-      <x:c r="B580" s="23"/>
+      <x:c r="A580"/>
+      <x:c r="B580"/>
       <x:c r="C580"/>
       <x:c r="D580"/>
       <x:c r="E580"/>
@@ -23778,8 +23778,8 @@
       <x:c r="G580"/>
     </x:row>
     <x:row r="581">
-      <x:c r="A581" s="23"/>
-      <x:c r="B581" s="23"/>
+      <x:c r="A581"/>
+      <x:c r="B581"/>
       <x:c r="C581"/>
       <x:c r="D581"/>
       <x:c r="E581"/>
@@ -23787,8 +23787,8 @@
       <x:c r="G581"/>
     </x:row>
     <x:row r="582">
-      <x:c r="A582" s="23"/>
-      <x:c r="B582" s="23"/>
+      <x:c r="A582"/>
+      <x:c r="B582"/>
       <x:c r="C582"/>
       <x:c r="D582"/>
       <x:c r="E582"/>
@@ -23796,8 +23796,8 @@
       <x:c r="G582"/>
     </x:row>
     <x:row r="583">
-      <x:c r="A583" s="23"/>
-      <x:c r="B583" s="23"/>
+      <x:c r="A583"/>
+      <x:c r="B583"/>
       <x:c r="C583"/>
       <x:c r="D583"/>
       <x:c r="E583"/>
@@ -23805,8 +23805,8 @@
       <x:c r="G583"/>
     </x:row>
     <x:row r="584">
-      <x:c r="A584" s="23"/>
-      <x:c r="B584" s="23"/>
+      <x:c r="A584"/>
+      <x:c r="B584"/>
       <x:c r="C584"/>
       <x:c r="D584"/>
       <x:c r="E584"/>
@@ -23814,8 +23814,8 @@
       <x:c r="G584"/>
     </x:row>
     <x:row r="585">
-      <x:c r="A585" s="23"/>
-      <x:c r="B585" s="23"/>
+      <x:c r="A585"/>
+      <x:c r="B585"/>
       <x:c r="C585"/>
       <x:c r="D585"/>
       <x:c r="E585"/>
@@ -23823,8 +23823,8 @@
       <x:c r="G585"/>
     </x:row>
     <x:row r="586">
-      <x:c r="A586" s="23"/>
-      <x:c r="B586" s="23"/>
+      <x:c r="A586"/>
+      <x:c r="B586"/>
       <x:c r="C586"/>
       <x:c r="D586"/>
       <x:c r="E586"/>
@@ -23832,8 +23832,8 @@
       <x:c r="G586"/>
     </x:row>
     <x:row r="587">
-      <x:c r="A587" s="23"/>
-      <x:c r="B587" s="23"/>
+      <x:c r="A587"/>
+      <x:c r="B587"/>
       <x:c r="C587"/>
       <x:c r="D587"/>
       <x:c r="E587"/>
@@ -23841,8 +23841,8 @@
       <x:c r="G587"/>
     </x:row>
     <x:row r="588">
-      <x:c r="A588" s="23"/>
-      <x:c r="B588" s="23"/>
+      <x:c r="A588"/>
+      <x:c r="B588"/>
       <x:c r="C588"/>
       <x:c r="D588"/>
       <x:c r="E588"/>
@@ -23850,8 +23850,8 @@
       <x:c r="G588"/>
     </x:row>
     <x:row r="589">
-      <x:c r="A589" s="23"/>
-      <x:c r="B589" s="23"/>
+      <x:c r="A589"/>
+      <x:c r="B589"/>
       <x:c r="C589"/>
       <x:c r="D589"/>
       <x:c r="E589"/>
@@ -23859,8 +23859,8 @@
       <x:c r="G589"/>
     </x:row>
     <x:row r="590">
-      <x:c r="A590" s="23"/>
-      <x:c r="B590" s="23"/>
+      <x:c r="A590"/>
+      <x:c r="B590"/>
       <x:c r="C590"/>
       <x:c r="D590"/>
       <x:c r="E590"/>
@@ -23868,8 +23868,8 @@
       <x:c r="G590"/>
     </x:row>
     <x:row r="591">
-      <x:c r="A591" s="23"/>
-      <x:c r="B591" s="23"/>
+      <x:c r="A591"/>
+      <x:c r="B591"/>
       <x:c r="C591"/>
       <x:c r="D591"/>
       <x:c r="E591"/>
@@ -23877,8 +23877,8 @@
       <x:c r="G591"/>
     </x:row>
     <x:row r="592">
-      <x:c r="A592" s="23"/>
-      <x:c r="B592" s="23"/>
+      <x:c r="A592"/>
+      <x:c r="B592"/>
       <x:c r="C592"/>
       <x:c r="D592"/>
       <x:c r="E592"/>
@@ -23886,8 +23886,8 @@
       <x:c r="G592"/>
     </x:row>
     <x:row r="593">
-      <x:c r="A593" s="23"/>
-      <x:c r="B593" s="23"/>
+      <x:c r="A593"/>
+      <x:c r="B593"/>
       <x:c r="C593"/>
       <x:c r="D593"/>
       <x:c r="E593"/>
@@ -23895,8 +23895,8 @@
       <x:c r="G593"/>
     </x:row>
     <x:row r="594">
-      <x:c r="A594" s="23"/>
-      <x:c r="B594" s="23"/>
+      <x:c r="A594"/>
+      <x:c r="B594"/>
       <x:c r="C594"/>
       <x:c r="D594"/>
       <x:c r="E594"/>
@@ -23904,8 +23904,8 @@
       <x:c r="G594"/>
     </x:row>
     <x:row r="595">
-      <x:c r="A595" s="23"/>
-      <x:c r="B595" s="23"/>
+      <x:c r="A595"/>
+      <x:c r="B595"/>
       <x:c r="C595"/>
       <x:c r="D595"/>
       <x:c r="E595"/>
@@ -23913,8 +23913,8 @@
       <x:c r="G595"/>
     </x:row>
     <x:row r="596">
-      <x:c r="A596" s="23"/>
-      <x:c r="B596" s="23"/>
+      <x:c r="A596"/>
+      <x:c r="B596"/>
       <x:c r="C596"/>
       <x:c r="D596"/>
       <x:c r="E596"/>
@@ -23922,8 +23922,8 @@
       <x:c r="G596"/>
     </x:row>
     <x:row r="597">
-      <x:c r="A597" s="23"/>
-      <x:c r="B597" s="23"/>
+      <x:c r="A597"/>
+      <x:c r="B597"/>
       <x:c r="C597"/>
       <x:c r="D597"/>
       <x:c r="E597"/>
@@ -23931,8 +23931,8 @@
       <x:c r="G597"/>
     </x:row>
     <x:row r="598">
-      <x:c r="A598" s="23"/>
-      <x:c r="B598" s="23"/>
+      <x:c r="A598"/>
+      <x:c r="B598"/>
       <x:c r="C598"/>
       <x:c r="D598"/>
       <x:c r="E598"/>
@@ -23940,8 +23940,8 @@
       <x:c r="G598"/>
     </x:row>
     <x:row r="599">
-      <x:c r="A599" s="23"/>
-      <x:c r="B599" s="23"/>
+      <x:c r="A599"/>
+      <x:c r="B599"/>
       <x:c r="C599"/>
       <x:c r="D599"/>
       <x:c r="E599"/>
@@ -23949,8 +23949,8 @@
       <x:c r="G599"/>
     </x:row>
     <x:row r="600">
-      <x:c r="A600" s="23"/>
-      <x:c r="B600" s="23"/>
+      <x:c r="A600"/>
+      <x:c r="B600"/>
       <x:c r="C600"/>
       <x:c r="D600"/>
       <x:c r="E600"/>
@@ -23958,8 +23958,8 @@
       <x:c r="G600"/>
     </x:row>
     <x:row r="601">
-      <x:c r="A601" s="23"/>
-      <x:c r="B601" s="23"/>
+      <x:c r="A601"/>
+      <x:c r="B601"/>
       <x:c r="C601"/>
       <x:c r="D601"/>
       <x:c r="E601"/>
@@ -23967,8 +23967,8 @@
       <x:c r="G601"/>
     </x:row>
     <x:row r="602">
-      <x:c r="A602" s="23"/>
-      <x:c r="B602" s="23"/>
+      <x:c r="A602"/>
+      <x:c r="B602"/>
       <x:c r="C602"/>
       <x:c r="D602"/>
       <x:c r="E602"/>
@@ -23976,8 +23976,8 @@
       <x:c r="G602"/>
     </x:row>
     <x:row r="603">
-      <x:c r="A603" s="23"/>
-      <x:c r="B603" s="23"/>
+      <x:c r="A603"/>
+      <x:c r="B603"/>
       <x:c r="C603"/>
       <x:c r="D603"/>
       <x:c r="E603"/>
@@ -23985,8 +23985,8 @@
       <x:c r="G603"/>
     </x:row>
     <x:row r="604">
-      <x:c r="A604" s="23"/>
-      <x:c r="B604" s="23"/>
+      <x:c r="A604"/>
+      <x:c r="B604"/>
       <x:c r="C604"/>
       <x:c r="D604"/>
       <x:c r="E604"/>
@@ -23994,8 +23994,8 @@
       <x:c r="G604"/>
     </x:row>
     <x:row r="605">
-      <x:c r="A605" s="23"/>
-      <x:c r="B605" s="23"/>
+      <x:c r="A605"/>
+      <x:c r="B605"/>
       <x:c r="C605"/>
       <x:c r="D605"/>
       <x:c r="E605"/>
@@ -24003,8 +24003,8 @@
       <x:c r="G605"/>
     </x:row>
     <x:row r="606">
-      <x:c r="A606" s="23"/>
-      <x:c r="B606" s="23"/>
+      <x:c r="A606"/>
+      <x:c r="B606"/>
       <x:c r="C606"/>
       <x:c r="D606"/>
       <x:c r="E606"/>
@@ -24012,8 +24012,8 @@
       <x:c r="G606"/>
     </x:row>
     <x:row r="607">
-      <x:c r="A607" s="23"/>
-      <x:c r="B607" s="23"/>
+      <x:c r="A607"/>
+      <x:c r="B607"/>
       <x:c r="C607"/>
       <x:c r="D607"/>
       <x:c r="E607"/>
@@ -24021,8 +24021,8 @@
       <x:c r="G607"/>
     </x:row>
     <x:row r="608">
-      <x:c r="A608" s="23"/>
-      <x:c r="B608" s="23"/>
+      <x:c r="A608"/>
+      <x:c r="B608"/>
       <x:c r="C608"/>
       <x:c r="D608"/>
       <x:c r="E608"/>
@@ -24030,16 +24030,16 @@
       <x:c r="G608"/>
     </x:row>
     <x:row r="609">
-      <x:c r="A609" s="23"/>
-      <x:c r="B609" s="23"/>
+      <x:c r="A609"/>
+      <x:c r="B609"/>
     </x:row>
     <x:row r="610">
-      <x:c r="A610" s="23"/>
-      <x:c r="B610" s="23"/>
+      <x:c r="A610"/>
+      <x:c r="B610"/>
     </x:row>
     <x:row r="611">
-      <x:c r="A611" s="23"/>
-      <x:c r="B611" s="23"/>
+      <x:c r="A611"/>
+      <x:c r="B611"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -32839,484 +32839,484 @@
       <x:c r="G415" s="52"/>
     </x:row>
     <x:row r="416">
-      <x:c r="A416" s="51"/>
-      <x:c r="B416" s="51"/>
-      <x:c r="C416" s="52"/>
-      <x:c r="D416" s="52"/>
-      <x:c r="E416" s="52"/>
-      <x:c r="F416" s="52"/>
-      <x:c r="G416" s="52"/>
+      <x:c r="A416"/>
+      <x:c r="B416"/>
+      <x:c r="C416"/>
+      <x:c r="D416"/>
+      <x:c r="E416"/>
+      <x:c r="F416"/>
+      <x:c r="G416"/>
     </x:row>
     <x:row r="417">
-      <x:c r="A417" s="51"/>
-      <x:c r="B417" s="51"/>
-      <x:c r="C417" s="52"/>
-      <x:c r="D417" s="52"/>
-      <x:c r="E417" s="52"/>
-      <x:c r="F417" s="52"/>
-      <x:c r="G417" s="52"/>
+      <x:c r="A417"/>
+      <x:c r="B417"/>
+      <x:c r="C417"/>
+      <x:c r="D417"/>
+      <x:c r="E417"/>
+      <x:c r="F417"/>
+      <x:c r="G417"/>
     </x:row>
     <x:row r="418">
-      <x:c r="A418" s="51"/>
-      <x:c r="B418" s="51"/>
-      <x:c r="C418" s="52"/>
-      <x:c r="D418" s="52"/>
-      <x:c r="E418" s="52"/>
-      <x:c r="F418" s="52"/>
-      <x:c r="G418" s="52"/>
+      <x:c r="A418"/>
+      <x:c r="B418"/>
+      <x:c r="C418"/>
+      <x:c r="D418"/>
+      <x:c r="E418"/>
+      <x:c r="F418"/>
+      <x:c r="G418"/>
     </x:row>
     <x:row r="419">
-      <x:c r="A419" s="51"/>
-      <x:c r="B419" s="51"/>
-      <x:c r="C419" s="52"/>
-      <x:c r="D419" s="52"/>
-      <x:c r="E419" s="52"/>
-      <x:c r="F419" s="52"/>
-      <x:c r="G419" s="52"/>
+      <x:c r="A419"/>
+      <x:c r="B419"/>
+      <x:c r="C419"/>
+      <x:c r="D419"/>
+      <x:c r="E419"/>
+      <x:c r="F419"/>
+      <x:c r="G419"/>
     </x:row>
     <x:row r="420">
-      <x:c r="A420" s="51"/>
-      <x:c r="B420" s="51"/>
-      <x:c r="C420" s="52"/>
-      <x:c r="D420" s="52"/>
-      <x:c r="E420" s="52"/>
-      <x:c r="F420" s="52"/>
-      <x:c r="G420" s="52"/>
+      <x:c r="A420"/>
+      <x:c r="B420"/>
+      <x:c r="C420"/>
+      <x:c r="D420"/>
+      <x:c r="E420"/>
+      <x:c r="F420"/>
+      <x:c r="G420"/>
     </x:row>
     <x:row r="421">
-      <x:c r="A421" s="51"/>
-      <x:c r="B421" s="51"/>
-      <x:c r="C421" s="52"/>
-      <x:c r="D421" s="52"/>
-      <x:c r="E421" s="52"/>
-      <x:c r="F421" s="52"/>
-      <x:c r="G421" s="52"/>
+      <x:c r="A421"/>
+      <x:c r="B421"/>
+      <x:c r="C421"/>
+      <x:c r="D421"/>
+      <x:c r="E421"/>
+      <x:c r="F421"/>
+      <x:c r="G421"/>
     </x:row>
     <x:row r="422">
-      <x:c r="A422" s="51"/>
-      <x:c r="B422" s="51"/>
-      <x:c r="C422" s="52"/>
-      <x:c r="D422" s="52"/>
-      <x:c r="E422" s="52"/>
-      <x:c r="F422" s="52"/>
-      <x:c r="G422" s="52"/>
+      <x:c r="A422"/>
+      <x:c r="B422"/>
+      <x:c r="C422"/>
+      <x:c r="D422"/>
+      <x:c r="E422"/>
+      <x:c r="F422"/>
+      <x:c r="G422"/>
     </x:row>
     <x:row r="423">
-      <x:c r="A423" s="51"/>
-      <x:c r="B423" s="51"/>
-      <x:c r="C423" s="52"/>
-      <x:c r="D423" s="52"/>
-      <x:c r="E423" s="52"/>
-      <x:c r="F423" s="52"/>
-      <x:c r="G423" s="52"/>
+      <x:c r="A423"/>
+      <x:c r="B423"/>
+      <x:c r="C423"/>
+      <x:c r="D423"/>
+      <x:c r="E423"/>
+      <x:c r="F423"/>
+      <x:c r="G423"/>
     </x:row>
     <x:row r="424">
-      <x:c r="A424" s="51"/>
-      <x:c r="B424" s="51"/>
-      <x:c r="C424" s="52"/>
-      <x:c r="D424" s="52"/>
-      <x:c r="E424" s="52"/>
-      <x:c r="F424" s="52"/>
-      <x:c r="G424" s="52"/>
+      <x:c r="A424"/>
+      <x:c r="B424"/>
+      <x:c r="C424"/>
+      <x:c r="D424"/>
+      <x:c r="E424"/>
+      <x:c r="F424"/>
+      <x:c r="G424"/>
     </x:row>
     <x:row r="425">
-      <x:c r="A425" s="51"/>
-      <x:c r="B425" s="51"/>
-      <x:c r="C425" s="52"/>
-      <x:c r="D425" s="52"/>
-      <x:c r="E425" s="52"/>
-      <x:c r="F425" s="52"/>
-      <x:c r="G425" s="52"/>
+      <x:c r="A425"/>
+      <x:c r="B425"/>
+      <x:c r="C425"/>
+      <x:c r="D425"/>
+      <x:c r="E425"/>
+      <x:c r="F425"/>
+      <x:c r="G425"/>
     </x:row>
     <x:row r="426">
-      <x:c r="A426" s="51"/>
-      <x:c r="B426" s="51"/>
-      <x:c r="C426" s="52"/>
-      <x:c r="D426" s="52"/>
-      <x:c r="E426" s="52"/>
-      <x:c r="F426" s="52"/>
-      <x:c r="G426" s="52"/>
+      <x:c r="A426"/>
+      <x:c r="B426"/>
+      <x:c r="C426"/>
+      <x:c r="D426"/>
+      <x:c r="E426"/>
+      <x:c r="F426"/>
+      <x:c r="G426"/>
     </x:row>
     <x:row r="427">
-      <x:c r="A427" s="51"/>
-      <x:c r="B427" s="51"/>
-      <x:c r="C427" s="52"/>
-      <x:c r="D427" s="52"/>
-      <x:c r="E427" s="52"/>
-      <x:c r="F427" s="52"/>
-      <x:c r="G427" s="52"/>
+      <x:c r="A427"/>
+      <x:c r="B427"/>
+      <x:c r="C427"/>
+      <x:c r="D427"/>
+      <x:c r="E427"/>
+      <x:c r="F427"/>
+      <x:c r="G427"/>
     </x:row>
     <x:row r="428">
-      <x:c r="A428" s="51"/>
-      <x:c r="B428" s="51"/>
-      <x:c r="C428" s="52"/>
-      <x:c r="D428" s="52"/>
-      <x:c r="E428" s="52"/>
-      <x:c r="F428" s="52"/>
-      <x:c r="G428" s="52"/>
+      <x:c r="A428"/>
+      <x:c r="B428"/>
+      <x:c r="C428"/>
+      <x:c r="D428"/>
+      <x:c r="E428"/>
+      <x:c r="F428"/>
+      <x:c r="G428"/>
     </x:row>
     <x:row r="429">
-      <x:c r="A429" s="51"/>
-      <x:c r="B429" s="51"/>
-      <x:c r="C429" s="52"/>
-      <x:c r="D429" s="52"/>
-      <x:c r="E429" s="52"/>
-      <x:c r="F429" s="52"/>
-      <x:c r="G429" s="52"/>
+      <x:c r="A429"/>
+      <x:c r="B429"/>
+      <x:c r="C429"/>
+      <x:c r="D429"/>
+      <x:c r="E429"/>
+      <x:c r="F429"/>
+      <x:c r="G429"/>
     </x:row>
     <x:row r="430">
-      <x:c r="A430" s="51"/>
-      <x:c r="B430" s="51"/>
-      <x:c r="C430" s="52"/>
-      <x:c r="D430" s="52"/>
-      <x:c r="E430" s="52"/>
-      <x:c r="F430" s="52"/>
-      <x:c r="G430" s="52"/>
+      <x:c r="A430"/>
+      <x:c r="B430"/>
+      <x:c r="C430"/>
+      <x:c r="D430"/>
+      <x:c r="E430"/>
+      <x:c r="F430"/>
+      <x:c r="G430"/>
     </x:row>
     <x:row r="431">
-      <x:c r="A431" s="51"/>
-      <x:c r="B431" s="51"/>
-      <x:c r="C431" s="52"/>
-      <x:c r="D431" s="52"/>
-      <x:c r="E431" s="52"/>
-      <x:c r="F431" s="52"/>
-      <x:c r="G431" s="52"/>
+      <x:c r="A431"/>
+      <x:c r="B431"/>
+      <x:c r="C431"/>
+      <x:c r="D431"/>
+      <x:c r="E431"/>
+      <x:c r="F431"/>
+      <x:c r="G431"/>
     </x:row>
     <x:row r="432">
-      <x:c r="A432" s="51"/>
-      <x:c r="B432" s="51"/>
-      <x:c r="C432" s="52"/>
-      <x:c r="D432" s="52"/>
-      <x:c r="E432" s="52"/>
-      <x:c r="F432" s="52"/>
-      <x:c r="G432" s="52"/>
+      <x:c r="A432"/>
+      <x:c r="B432"/>
+      <x:c r="C432"/>
+      <x:c r="D432"/>
+      <x:c r="E432"/>
+      <x:c r="F432"/>
+      <x:c r="G432"/>
     </x:row>
     <x:row r="433">
-      <x:c r="A433" s="51"/>
-      <x:c r="B433" s="51"/>
-      <x:c r="C433" s="52"/>
-      <x:c r="D433" s="52"/>
-      <x:c r="E433" s="52"/>
-      <x:c r="F433" s="52"/>
-      <x:c r="G433" s="52"/>
+      <x:c r="A433"/>
+      <x:c r="B433"/>
+      <x:c r="C433"/>
+      <x:c r="D433"/>
+      <x:c r="E433"/>
+      <x:c r="F433"/>
+      <x:c r="G433"/>
     </x:row>
     <x:row r="434">
-      <x:c r="A434" s="51"/>
-      <x:c r="B434" s="51"/>
-      <x:c r="C434" s="52"/>
-      <x:c r="D434" s="52"/>
-      <x:c r="E434" s="52"/>
-      <x:c r="F434" s="52"/>
-      <x:c r="G434" s="52"/>
+      <x:c r="A434"/>
+      <x:c r="B434"/>
+      <x:c r="C434"/>
+      <x:c r="D434"/>
+      <x:c r="E434"/>
+      <x:c r="F434"/>
+      <x:c r="G434"/>
     </x:row>
     <x:row r="435">
-      <x:c r="A435" s="51"/>
-      <x:c r="B435" s="51"/>
-      <x:c r="C435" s="52"/>
-      <x:c r="D435" s="52"/>
-      <x:c r="E435" s="52"/>
-      <x:c r="F435" s="52"/>
-      <x:c r="G435" s="52"/>
+      <x:c r="A435"/>
+      <x:c r="B435"/>
+      <x:c r="C435"/>
+      <x:c r="D435"/>
+      <x:c r="E435"/>
+      <x:c r="F435"/>
+      <x:c r="G435"/>
     </x:row>
     <x:row r="436">
-      <x:c r="A436" s="51"/>
-      <x:c r="B436" s="51"/>
-      <x:c r="C436" s="52"/>
-      <x:c r="D436" s="52"/>
-      <x:c r="E436" s="52"/>
-      <x:c r="F436" s="52"/>
-      <x:c r="G436" s="52"/>
+      <x:c r="A436"/>
+      <x:c r="B436"/>
+      <x:c r="C436"/>
+      <x:c r="D436"/>
+      <x:c r="E436"/>
+      <x:c r="F436"/>
+      <x:c r="G436"/>
     </x:row>
     <x:row r="437">
-      <x:c r="A437" s="51"/>
-      <x:c r="B437" s="51"/>
-      <x:c r="C437" s="52"/>
-      <x:c r="D437" s="52"/>
-      <x:c r="E437" s="52"/>
-      <x:c r="F437" s="52"/>
-      <x:c r="G437" s="52"/>
+      <x:c r="A437"/>
+      <x:c r="B437"/>
+      <x:c r="C437"/>
+      <x:c r="D437"/>
+      <x:c r="E437"/>
+      <x:c r="F437"/>
+      <x:c r="G437"/>
     </x:row>
     <x:row r="438">
-      <x:c r="A438" s="51"/>
-      <x:c r="B438" s="51"/>
-      <x:c r="C438" s="52"/>
-      <x:c r="D438" s="52"/>
-      <x:c r="E438" s="52"/>
-      <x:c r="F438" s="52"/>
-      <x:c r="G438" s="52"/>
+      <x:c r="A438"/>
+      <x:c r="B438"/>
+      <x:c r="C438"/>
+      <x:c r="D438"/>
+      <x:c r="E438"/>
+      <x:c r="F438"/>
+      <x:c r="G438"/>
     </x:row>
     <x:row r="439">
-      <x:c r="A439" s="51"/>
-      <x:c r="B439" s="51"/>
-      <x:c r="C439" s="52"/>
-      <x:c r="D439" s="52"/>
-      <x:c r="E439" s="52"/>
-      <x:c r="F439" s="52"/>
-      <x:c r="G439" s="52"/>
+      <x:c r="A439"/>
+      <x:c r="B439"/>
+      <x:c r="C439"/>
+      <x:c r="D439"/>
+      <x:c r="E439"/>
+      <x:c r="F439"/>
+      <x:c r="G439"/>
     </x:row>
     <x:row r="440">
-      <x:c r="A440" s="51"/>
-      <x:c r="B440" s="51"/>
-      <x:c r="C440" s="52"/>
-      <x:c r="D440" s="52"/>
-      <x:c r="E440" s="52"/>
-      <x:c r="F440" s="52"/>
-      <x:c r="G440" s="52"/>
+      <x:c r="A440"/>
+      <x:c r="B440"/>
+      <x:c r="C440"/>
+      <x:c r="D440"/>
+      <x:c r="E440"/>
+      <x:c r="F440"/>
+      <x:c r="G440"/>
     </x:row>
     <x:row r="441">
-      <x:c r="A441" s="51"/>
-      <x:c r="B441" s="51"/>
-      <x:c r="C441" s="52"/>
-      <x:c r="D441" s="52"/>
-      <x:c r="E441" s="52"/>
-      <x:c r="F441" s="52"/>
-      <x:c r="G441" s="52"/>
+      <x:c r="A441"/>
+      <x:c r="B441"/>
+      <x:c r="C441"/>
+      <x:c r="D441"/>
+      <x:c r="E441"/>
+      <x:c r="F441"/>
+      <x:c r="G441"/>
     </x:row>
     <x:row r="442">
-      <x:c r="A442" s="51"/>
-      <x:c r="B442" s="51"/>
-      <x:c r="C442" s="52"/>
-      <x:c r="D442" s="52"/>
-      <x:c r="E442" s="52"/>
-      <x:c r="F442" s="52"/>
-      <x:c r="G442" s="52"/>
+      <x:c r="A442"/>
+      <x:c r="B442"/>
+      <x:c r="C442"/>
+      <x:c r="D442"/>
+      <x:c r="E442"/>
+      <x:c r="F442"/>
+      <x:c r="G442"/>
     </x:row>
     <x:row r="443">
-      <x:c r="A443" s="51"/>
-      <x:c r="B443" s="51"/>
-      <x:c r="C443" s="52"/>
-      <x:c r="D443" s="52"/>
-      <x:c r="E443" s="52"/>
-      <x:c r="F443" s="52"/>
-      <x:c r="G443" s="52"/>
+      <x:c r="A443"/>
+      <x:c r="B443"/>
+      <x:c r="C443"/>
+      <x:c r="D443"/>
+      <x:c r="E443"/>
+      <x:c r="F443"/>
+      <x:c r="G443"/>
     </x:row>
     <x:row r="444">
-      <x:c r="A444" s="23"/>
-      <x:c r="B444" s="23"/>
+      <x:c r="A444"/>
+      <x:c r="B444"/>
     </x:row>
     <x:row r="445">
-      <x:c r="A445" s="23"/>
-      <x:c r="B445" s="23"/>
+      <x:c r="A445"/>
+      <x:c r="B445"/>
     </x:row>
     <x:row r="446">
-      <x:c r="A446" s="23"/>
-      <x:c r="B446" s="23"/>
+      <x:c r="A446"/>
+      <x:c r="B446"/>
     </x:row>
     <x:row r="447">
-      <x:c r="A447" s="23"/>
-      <x:c r="B447" s="23"/>
+      <x:c r="A447"/>
+      <x:c r="B447"/>
     </x:row>
     <x:row r="448">
-      <x:c r="A448" s="23"/>
-      <x:c r="B448" s="23"/>
+      <x:c r="A448"/>
+      <x:c r="B448"/>
     </x:row>
     <x:row r="449">
-      <x:c r="A449" s="23"/>
-      <x:c r="B449" s="23"/>
+      <x:c r="A449"/>
+      <x:c r="B449"/>
     </x:row>
     <x:row r="450">
-      <x:c r="A450" s="23"/>
-      <x:c r="B450" s="23"/>
+      <x:c r="A450"/>
+      <x:c r="B450"/>
     </x:row>
     <x:row r="451">
-      <x:c r="A451" s="23"/>
-      <x:c r="B451" s="23"/>
+      <x:c r="A451"/>
+      <x:c r="B451"/>
     </x:row>
     <x:row r="452">
-      <x:c r="A452" s="23"/>
-      <x:c r="B452" s="23"/>
+      <x:c r="A452"/>
+      <x:c r="B452"/>
     </x:row>
     <x:row r="453">
-      <x:c r="A453" s="23"/>
-      <x:c r="B453" s="23"/>
+      <x:c r="A453"/>
+      <x:c r="B453"/>
     </x:row>
     <x:row r="454">
-      <x:c r="A454" s="23"/>
-      <x:c r="B454" s="23"/>
+      <x:c r="A454"/>
+      <x:c r="B454"/>
     </x:row>
     <x:row r="455">
-      <x:c r="A455" s="23"/>
-      <x:c r="B455" s="23"/>
+      <x:c r="A455"/>
+      <x:c r="B455"/>
     </x:row>
     <x:row r="456">
-      <x:c r="A456" s="23"/>
-      <x:c r="B456" s="23"/>
+      <x:c r="A456"/>
+      <x:c r="B456"/>
     </x:row>
     <x:row r="457">
-      <x:c r="A457" s="23"/>
-      <x:c r="B457" s="23"/>
+      <x:c r="A457"/>
+      <x:c r="B457"/>
     </x:row>
     <x:row r="458">
-      <x:c r="A458" s="23"/>
-      <x:c r="B458" s="23"/>
+      <x:c r="A458"/>
+      <x:c r="B458"/>
     </x:row>
     <x:row r="459">
-      <x:c r="A459" s="23"/>
-      <x:c r="B459" s="23"/>
+      <x:c r="A459"/>
+      <x:c r="B459"/>
     </x:row>
     <x:row r="460">
-      <x:c r="A460" s="23"/>
-      <x:c r="B460" s="23"/>
+      <x:c r="A460"/>
+      <x:c r="B460"/>
     </x:row>
     <x:row r="461">
-      <x:c r="A461" s="23"/>
-      <x:c r="B461" s="23"/>
+      <x:c r="A461"/>
+      <x:c r="B461"/>
     </x:row>
     <x:row r="462">
-      <x:c r="A462" s="23"/>
-      <x:c r="B462" s="23"/>
+      <x:c r="A462"/>
+      <x:c r="B462"/>
     </x:row>
     <x:row r="463">
-      <x:c r="A463" s="23"/>
-      <x:c r="B463" s="23"/>
+      <x:c r="A463"/>
+      <x:c r="B463"/>
     </x:row>
     <x:row r="464">
-      <x:c r="A464" s="23"/>
-      <x:c r="B464" s="23"/>
+      <x:c r="A464"/>
+      <x:c r="B464"/>
     </x:row>
     <x:row r="465">
-      <x:c r="A465" s="23"/>
-      <x:c r="B465" s="23"/>
+      <x:c r="A465"/>
+      <x:c r="B465"/>
     </x:row>
     <x:row r="466">
-      <x:c r="A466" s="23"/>
-      <x:c r="B466" s="23"/>
+      <x:c r="A466"/>
+      <x:c r="B466"/>
     </x:row>
     <x:row r="467">
-      <x:c r="A467" s="23"/>
-      <x:c r="B467" s="23"/>
+      <x:c r="A467"/>
+      <x:c r="B467"/>
     </x:row>
     <x:row r="468">
-      <x:c r="A468" s="23"/>
-      <x:c r="B468" s="23"/>
+      <x:c r="A468"/>
+      <x:c r="B468"/>
     </x:row>
     <x:row r="469">
-      <x:c r="A469" s="23"/>
-      <x:c r="B469" s="23"/>
+      <x:c r="A469"/>
+      <x:c r="B469"/>
     </x:row>
     <x:row r="470">
-      <x:c r="A470" s="23"/>
-      <x:c r="B470" s="23"/>
+      <x:c r="A470"/>
+      <x:c r="B470"/>
     </x:row>
     <x:row r="471">
-      <x:c r="A471" s="23"/>
-      <x:c r="B471" s="23"/>
+      <x:c r="A471"/>
+      <x:c r="B471"/>
     </x:row>
     <x:row r="472">
-      <x:c r="A472" s="23"/>
-      <x:c r="B472" s="23"/>
+      <x:c r="A472"/>
+      <x:c r="B472"/>
     </x:row>
     <x:row r="473">
-      <x:c r="A473" s="23"/>
-      <x:c r="B473" s="23"/>
+      <x:c r="A473"/>
+      <x:c r="B473"/>
     </x:row>
     <x:row r="474">
-      <x:c r="A474" s="23"/>
-      <x:c r="B474" s="23"/>
+      <x:c r="A474"/>
+      <x:c r="B474"/>
     </x:row>
     <x:row r="475">
-      <x:c r="A475" s="23"/>
-      <x:c r="B475" s="23"/>
+      <x:c r="A475"/>
+      <x:c r="B475"/>
     </x:row>
     <x:row r="476">
-      <x:c r="A476" s="23"/>
-      <x:c r="B476" s="23"/>
+      <x:c r="A476"/>
+      <x:c r="B476"/>
     </x:row>
     <x:row r="477">
-      <x:c r="A477" s="23"/>
-      <x:c r="B477" s="23"/>
+      <x:c r="A477"/>
+      <x:c r="B477"/>
     </x:row>
     <x:row r="478">
-      <x:c r="A478" s="23"/>
-      <x:c r="B478" s="23"/>
+      <x:c r="A478"/>
+      <x:c r="B478"/>
     </x:row>
     <x:row r="479">
-      <x:c r="A479" s="23"/>
-      <x:c r="B479" s="23"/>
+      <x:c r="A479"/>
+      <x:c r="B479"/>
     </x:row>
     <x:row r="480">
-      <x:c r="A480" s="23"/>
-      <x:c r="B480" s="23"/>
+      <x:c r="A480"/>
+      <x:c r="B480"/>
     </x:row>
     <x:row r="481">
-      <x:c r="A481" s="23"/>
-      <x:c r="B481" s="23"/>
+      <x:c r="A481"/>
+      <x:c r="B481"/>
     </x:row>
     <x:row r="482">
-      <x:c r="A482" s="23"/>
-      <x:c r="B482" s="23"/>
+      <x:c r="A482"/>
+      <x:c r="B482"/>
     </x:row>
     <x:row r="483">
-      <x:c r="A483" s="23"/>
-      <x:c r="B483" s="23"/>
+      <x:c r="A483"/>
+      <x:c r="B483"/>
     </x:row>
     <x:row r="484">
-      <x:c r="A484" s="23"/>
-      <x:c r="B484" s="23"/>
+      <x:c r="A484"/>
+      <x:c r="B484"/>
     </x:row>
     <x:row r="485">
-      <x:c r="A485" s="23"/>
-      <x:c r="B485" s="23"/>
+      <x:c r="A485"/>
+      <x:c r="B485"/>
     </x:row>
     <x:row r="486">
-      <x:c r="A486" s="23"/>
-      <x:c r="B486" s="23"/>
+      <x:c r="A486"/>
+      <x:c r="B486"/>
     </x:row>
     <x:row r="487">
-      <x:c r="A487" s="23"/>
-      <x:c r="B487" s="23"/>
+      <x:c r="A487"/>
+      <x:c r="B487"/>
     </x:row>
     <x:row r="488">
-      <x:c r="A488" s="23"/>
-      <x:c r="B488" s="23"/>
+      <x:c r="A488"/>
+      <x:c r="B488"/>
     </x:row>
     <x:row r="489">
-      <x:c r="A489" s="23"/>
-      <x:c r="B489" s="23"/>
+      <x:c r="A489"/>
+      <x:c r="B489"/>
     </x:row>
     <x:row r="490">
-      <x:c r="A490" s="23"/>
-      <x:c r="B490" s="23"/>
+      <x:c r="A490"/>
+      <x:c r="B490"/>
     </x:row>
     <x:row r="491">
-      <x:c r="A491" s="23"/>
-      <x:c r="B491" s="23"/>
+      <x:c r="A491"/>
+      <x:c r="B491"/>
     </x:row>
     <x:row r="492">
-      <x:c r="A492" s="23"/>
-      <x:c r="B492" s="23"/>
+      <x:c r="A492"/>
+      <x:c r="B492"/>
     </x:row>
     <x:row r="493">
-      <x:c r="A493" s="23"/>
-      <x:c r="B493" s="23"/>
+      <x:c r="A493"/>
+      <x:c r="B493"/>
     </x:row>
     <x:row r="494">
-      <x:c r="A494" s="23"/>
-      <x:c r="B494" s="23"/>
+      <x:c r="A494"/>
+      <x:c r="B494"/>
     </x:row>
     <x:row r="495">
-      <x:c r="A495" s="23"/>
-      <x:c r="B495" s="23"/>
+      <x:c r="A495"/>
+      <x:c r="B495"/>
     </x:row>
     <x:row r="496">
-      <x:c r="A496" s="23"/>
-      <x:c r="B496" s="23"/>
+      <x:c r="A496"/>
+      <x:c r="B496"/>
     </x:row>
     <x:row r="497">
-      <x:c r="A497" s="23"/>
-      <x:c r="B497" s="23"/>
+      <x:c r="A497"/>
+      <x:c r="B497"/>
     </x:row>
     <x:row r="498">
-      <x:c r="A498" s="23"/>
-      <x:c r="B498" s="23"/>
+      <x:c r="A498"/>
+      <x:c r="B498"/>
     </x:row>
     <x:row r="499">
-      <x:c r="A499" s="23"/>
-      <x:c r="B499" s="23"/>
+      <x:c r="A499"/>
+      <x:c r="B499"/>
     </x:row>
     <x:row r="500">
-      <x:c r="A500" s="23"/>
-      <x:c r="B500" s="23"/>
+      <x:c r="A500"/>
+      <x:c r="B500"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -42231,505 +42231,505 @@
       <x:c r="G420" s="52"/>
     </x:row>
     <x:row r="421">
-      <x:c r="A421" s="51"/>
-      <x:c r="B421" s="51"/>
-      <x:c r="C421" s="52"/>
-      <x:c r="D421" s="52"/>
-      <x:c r="E421" s="52"/>
-      <x:c r="F421" s="52"/>
-      <x:c r="G421" s="52"/>
+      <x:c r="A421"/>
+      <x:c r="B421"/>
+      <x:c r="C421"/>
+      <x:c r="D421"/>
+      <x:c r="E421"/>
+      <x:c r="F421"/>
+      <x:c r="G421"/>
     </x:row>
     <x:row r="422">
-      <x:c r="A422" s="51"/>
-      <x:c r="B422" s="51"/>
-      <x:c r="C422" s="52"/>
-      <x:c r="D422" s="52"/>
-      <x:c r="E422" s="52"/>
-      <x:c r="F422" s="52"/>
-      <x:c r="G422" s="52"/>
+      <x:c r="A422"/>
+      <x:c r="B422"/>
+      <x:c r="C422"/>
+      <x:c r="D422"/>
+      <x:c r="E422"/>
+      <x:c r="F422"/>
+      <x:c r="G422"/>
     </x:row>
     <x:row r="423">
-      <x:c r="A423" s="51"/>
-      <x:c r="B423" s="51"/>
-      <x:c r="C423" s="52"/>
-      <x:c r="D423" s="52"/>
-      <x:c r="E423" s="52"/>
-      <x:c r="F423" s="52"/>
-      <x:c r="G423" s="52"/>
+      <x:c r="A423"/>
+      <x:c r="B423"/>
+      <x:c r="C423"/>
+      <x:c r="D423"/>
+      <x:c r="E423"/>
+      <x:c r="F423"/>
+      <x:c r="G423"/>
     </x:row>
     <x:row r="424">
-      <x:c r="A424" s="51"/>
-      <x:c r="B424" s="51"/>
-      <x:c r="C424" s="52"/>
-      <x:c r="D424" s="52"/>
-      <x:c r="E424" s="52"/>
-      <x:c r="F424" s="52"/>
-      <x:c r="G424" s="52"/>
+      <x:c r="A424"/>
+      <x:c r="B424"/>
+      <x:c r="C424"/>
+      <x:c r="D424"/>
+      <x:c r="E424"/>
+      <x:c r="F424"/>
+      <x:c r="G424"/>
     </x:row>
     <x:row r="425">
-      <x:c r="A425" s="51"/>
-      <x:c r="B425" s="51"/>
-      <x:c r="C425" s="52"/>
-      <x:c r="D425" s="52"/>
-      <x:c r="E425" s="52"/>
-      <x:c r="F425" s="52"/>
-      <x:c r="G425" s="52"/>
+      <x:c r="A425"/>
+      <x:c r="B425"/>
+      <x:c r="C425"/>
+      <x:c r="D425"/>
+      <x:c r="E425"/>
+      <x:c r="F425"/>
+      <x:c r="G425"/>
     </x:row>
     <x:row r="426">
-      <x:c r="A426" s="51"/>
-      <x:c r="B426" s="51"/>
-      <x:c r="C426" s="52"/>
-      <x:c r="D426" s="52"/>
-      <x:c r="E426" s="52"/>
-      <x:c r="F426" s="52"/>
-      <x:c r="G426" s="52"/>
+      <x:c r="A426"/>
+      <x:c r="B426"/>
+      <x:c r="C426"/>
+      <x:c r="D426"/>
+      <x:c r="E426"/>
+      <x:c r="F426"/>
+      <x:c r="G426"/>
     </x:row>
     <x:row r="427">
-      <x:c r="A427" s="51"/>
-      <x:c r="B427" s="51"/>
-      <x:c r="C427" s="52"/>
-      <x:c r="D427" s="52"/>
-      <x:c r="E427" s="52"/>
-      <x:c r="F427" s="52"/>
-      <x:c r="G427" s="52"/>
+      <x:c r="A427"/>
+      <x:c r="B427"/>
+      <x:c r="C427"/>
+      <x:c r="D427"/>
+      <x:c r="E427"/>
+      <x:c r="F427"/>
+      <x:c r="G427"/>
     </x:row>
     <x:row r="428">
-      <x:c r="A428" s="51"/>
-      <x:c r="B428" s="51"/>
-      <x:c r="C428" s="52"/>
-      <x:c r="D428" s="52"/>
-      <x:c r="E428" s="52"/>
-      <x:c r="F428" s="52"/>
-      <x:c r="G428" s="52"/>
+      <x:c r="A428"/>
+      <x:c r="B428"/>
+      <x:c r="C428"/>
+      <x:c r="D428"/>
+      <x:c r="E428"/>
+      <x:c r="F428"/>
+      <x:c r="G428"/>
     </x:row>
     <x:row r="429">
-      <x:c r="A429" s="51"/>
-      <x:c r="B429" s="51"/>
-      <x:c r="C429" s="52"/>
-      <x:c r="D429" s="52"/>
-      <x:c r="E429" s="52"/>
-      <x:c r="F429" s="52"/>
-      <x:c r="G429" s="52"/>
+      <x:c r="A429"/>
+      <x:c r="B429"/>
+      <x:c r="C429"/>
+      <x:c r="D429"/>
+      <x:c r="E429"/>
+      <x:c r="F429"/>
+      <x:c r="G429"/>
     </x:row>
     <x:row r="430">
-      <x:c r="A430" s="51"/>
-      <x:c r="B430" s="51"/>
-      <x:c r="C430" s="52"/>
-      <x:c r="D430" s="52"/>
-      <x:c r="E430" s="52"/>
-      <x:c r="F430" s="52"/>
-      <x:c r="G430" s="52"/>
+      <x:c r="A430"/>
+      <x:c r="B430"/>
+      <x:c r="C430"/>
+      <x:c r="D430"/>
+      <x:c r="E430"/>
+      <x:c r="F430"/>
+      <x:c r="G430"/>
     </x:row>
     <x:row r="431">
-      <x:c r="A431" s="51"/>
-      <x:c r="B431" s="51"/>
-      <x:c r="C431" s="52"/>
-      <x:c r="D431" s="52"/>
-      <x:c r="E431" s="52"/>
-      <x:c r="F431" s="52"/>
-      <x:c r="G431" s="52"/>
+      <x:c r="A431"/>
+      <x:c r="B431"/>
+      <x:c r="C431"/>
+      <x:c r="D431"/>
+      <x:c r="E431"/>
+      <x:c r="F431"/>
+      <x:c r="G431"/>
     </x:row>
     <x:row r="432">
-      <x:c r="A432" s="51"/>
-      <x:c r="B432" s="51"/>
-      <x:c r="C432" s="52"/>
-      <x:c r="D432" s="52"/>
-      <x:c r="E432" s="52"/>
-      <x:c r="F432" s="52"/>
-      <x:c r="G432" s="52"/>
+      <x:c r="A432"/>
+      <x:c r="B432"/>
+      <x:c r="C432"/>
+      <x:c r="D432"/>
+      <x:c r="E432"/>
+      <x:c r="F432"/>
+      <x:c r="G432"/>
     </x:row>
     <x:row r="433">
-      <x:c r="A433" s="51"/>
-      <x:c r="B433" s="51"/>
-      <x:c r="C433" s="52"/>
-      <x:c r="D433" s="52"/>
-      <x:c r="E433" s="52"/>
-      <x:c r="F433" s="52"/>
-      <x:c r="G433" s="52"/>
+      <x:c r="A433"/>
+      <x:c r="B433"/>
+      <x:c r="C433"/>
+      <x:c r="D433"/>
+      <x:c r="E433"/>
+      <x:c r="F433"/>
+      <x:c r="G433"/>
     </x:row>
     <x:row r="434">
-      <x:c r="A434" s="51"/>
-      <x:c r="B434" s="51"/>
-      <x:c r="C434" s="52"/>
-      <x:c r="D434" s="52"/>
-      <x:c r="E434" s="52"/>
-      <x:c r="F434" s="52"/>
-      <x:c r="G434" s="52"/>
+      <x:c r="A434"/>
+      <x:c r="B434"/>
+      <x:c r="C434"/>
+      <x:c r="D434"/>
+      <x:c r="E434"/>
+      <x:c r="F434"/>
+      <x:c r="G434"/>
     </x:row>
     <x:row r="435">
-      <x:c r="A435" s="51"/>
-      <x:c r="B435" s="51"/>
-      <x:c r="C435" s="52"/>
-      <x:c r="D435" s="52"/>
-      <x:c r="E435" s="52"/>
-      <x:c r="F435" s="52"/>
-      <x:c r="G435" s="52"/>
+      <x:c r="A435"/>
+      <x:c r="B435"/>
+      <x:c r="C435"/>
+      <x:c r="D435"/>
+      <x:c r="E435"/>
+      <x:c r="F435"/>
+      <x:c r="G435"/>
     </x:row>
     <x:row r="436">
-      <x:c r="A436" s="51"/>
-      <x:c r="B436" s="51"/>
-      <x:c r="C436" s="52"/>
-      <x:c r="D436" s="52"/>
-      <x:c r="E436" s="52"/>
-      <x:c r="F436" s="52"/>
-      <x:c r="G436" s="52"/>
+      <x:c r="A436"/>
+      <x:c r="B436"/>
+      <x:c r="C436"/>
+      <x:c r="D436"/>
+      <x:c r="E436"/>
+      <x:c r="F436"/>
+      <x:c r="G436"/>
     </x:row>
     <x:row r="437">
-      <x:c r="A437" s="51"/>
-      <x:c r="B437" s="51"/>
-      <x:c r="C437" s="52"/>
-      <x:c r="D437" s="52"/>
-      <x:c r="E437" s="52"/>
-      <x:c r="F437" s="52"/>
-      <x:c r="G437" s="52"/>
+      <x:c r="A437"/>
+      <x:c r="B437"/>
+      <x:c r="C437"/>
+      <x:c r="D437"/>
+      <x:c r="E437"/>
+      <x:c r="F437"/>
+      <x:c r="G437"/>
     </x:row>
     <x:row r="438">
-      <x:c r="A438" s="51"/>
-      <x:c r="B438" s="51"/>
-      <x:c r="C438" s="52"/>
-      <x:c r="D438" s="52"/>
-      <x:c r="E438" s="52"/>
-      <x:c r="F438" s="52"/>
-      <x:c r="G438" s="52"/>
+      <x:c r="A438"/>
+      <x:c r="B438"/>
+      <x:c r="C438"/>
+      <x:c r="D438"/>
+      <x:c r="E438"/>
+      <x:c r="F438"/>
+      <x:c r="G438"/>
     </x:row>
     <x:row r="439">
-      <x:c r="A439" s="51"/>
-      <x:c r="B439" s="51"/>
-      <x:c r="C439" s="52"/>
-      <x:c r="D439" s="52"/>
-      <x:c r="E439" s="52"/>
-      <x:c r="F439" s="52"/>
-      <x:c r="G439" s="52"/>
+      <x:c r="A439"/>
+      <x:c r="B439"/>
+      <x:c r="C439"/>
+      <x:c r="D439"/>
+      <x:c r="E439"/>
+      <x:c r="F439"/>
+      <x:c r="G439"/>
     </x:row>
     <x:row r="440">
-      <x:c r="A440" s="51"/>
-      <x:c r="B440" s="51"/>
-      <x:c r="C440" s="52"/>
-      <x:c r="D440" s="52"/>
-      <x:c r="E440" s="52"/>
-      <x:c r="F440" s="52"/>
-      <x:c r="G440" s="52"/>
+      <x:c r="A440"/>
+      <x:c r="B440"/>
+      <x:c r="C440"/>
+      <x:c r="D440"/>
+      <x:c r="E440"/>
+      <x:c r="F440"/>
+      <x:c r="G440"/>
     </x:row>
     <x:row r="441">
-      <x:c r="A441" s="51"/>
-      <x:c r="B441" s="51"/>
-      <x:c r="C441" s="52"/>
-      <x:c r="D441" s="52"/>
-      <x:c r="E441" s="52"/>
-      <x:c r="F441" s="52"/>
-      <x:c r="G441" s="52"/>
+      <x:c r="A441"/>
+      <x:c r="B441"/>
+      <x:c r="C441"/>
+      <x:c r="D441"/>
+      <x:c r="E441"/>
+      <x:c r="F441"/>
+      <x:c r="G441"/>
     </x:row>
     <x:row r="442">
-      <x:c r="A442" s="23"/>
-      <x:c r="B442" s="23"/>
+      <x:c r="A442"/>
+      <x:c r="B442"/>
       <x:c r="C442"/>
       <x:c r="D442"/>
       <x:c r="E442"/>
       <x:c r="F442"/>
     </x:row>
     <x:row r="443">
-      <x:c r="A443" s="23"/>
-      <x:c r="B443" s="23"/>
+      <x:c r="A443"/>
+      <x:c r="B443"/>
       <x:c r="C443"/>
       <x:c r="D443"/>
       <x:c r="E443"/>
       <x:c r="F443"/>
     </x:row>
     <x:row r="444">
-      <x:c r="A444" s="23"/>
-      <x:c r="B444" s="23"/>
+      <x:c r="A444"/>
+      <x:c r="B444"/>
       <x:c r="C444"/>
       <x:c r="D444"/>
       <x:c r="E444"/>
       <x:c r="F444"/>
     </x:row>
     <x:row r="445">
-      <x:c r="A445" s="23"/>
-      <x:c r="B445" s="23"/>
+      <x:c r="A445"/>
+      <x:c r="B445"/>
       <x:c r="C445"/>
       <x:c r="D445"/>
       <x:c r="E445"/>
       <x:c r="F445"/>
     </x:row>
     <x:row r="446">
-      <x:c r="A446" s="23"/>
-      <x:c r="B446" s="23"/>
+      <x:c r="A446"/>
+      <x:c r="B446"/>
     </x:row>
     <x:row r="447">
-      <x:c r="A447" s="23"/>
-      <x:c r="B447" s="23"/>
+      <x:c r="A447"/>
+      <x:c r="B447"/>
     </x:row>
     <x:row r="448">
-      <x:c r="A448" s="23"/>
-      <x:c r="B448" s="23"/>
+      <x:c r="A448"/>
+      <x:c r="B448"/>
     </x:row>
     <x:row r="449">
-      <x:c r="A449" s="23"/>
-      <x:c r="B449" s="23"/>
+      <x:c r="A449"/>
+      <x:c r="B449"/>
     </x:row>
     <x:row r="450">
-      <x:c r="A450" s="23"/>
-      <x:c r="B450" s="23"/>
+      <x:c r="A450"/>
+      <x:c r="B450"/>
     </x:row>
     <x:row r="451">
-      <x:c r="A451" s="23"/>
-      <x:c r="B451" s="23"/>
+      <x:c r="A451"/>
+      <x:c r="B451"/>
     </x:row>
     <x:row r="452">
-      <x:c r="A452" s="23"/>
-      <x:c r="B452" s="23"/>
+      <x:c r="A452"/>
+      <x:c r="B452"/>
     </x:row>
     <x:row r="453">
-      <x:c r="A453" s="23"/>
-      <x:c r="B453" s="23"/>
+      <x:c r="A453"/>
+      <x:c r="B453"/>
     </x:row>
     <x:row r="454">
-      <x:c r="A454" s="23"/>
-      <x:c r="B454" s="23"/>
+      <x:c r="A454"/>
+      <x:c r="B454"/>
     </x:row>
     <x:row r="455">
-      <x:c r="A455" s="23"/>
-      <x:c r="B455" s="23"/>
+      <x:c r="A455"/>
+      <x:c r="B455"/>
     </x:row>
     <x:row r="456">
-      <x:c r="A456" s="23"/>
-      <x:c r="B456" s="23"/>
+      <x:c r="A456"/>
+      <x:c r="B456"/>
     </x:row>
     <x:row r="457">
-      <x:c r="A457" s="23"/>
-      <x:c r="B457" s="23"/>
+      <x:c r="A457"/>
+      <x:c r="B457"/>
     </x:row>
     <x:row r="458">
-      <x:c r="A458" s="23"/>
-      <x:c r="B458" s="23"/>
+      <x:c r="A458"/>
+      <x:c r="B458"/>
     </x:row>
     <x:row r="459">
-      <x:c r="A459" s="23"/>
-      <x:c r="B459" s="23"/>
+      <x:c r="A459"/>
+      <x:c r="B459"/>
     </x:row>
     <x:row r="460">
-      <x:c r="A460" s="23"/>
-      <x:c r="B460" s="23"/>
+      <x:c r="A460"/>
+      <x:c r="B460"/>
     </x:row>
     <x:row r="461">
-      <x:c r="A461" s="23"/>
-      <x:c r="B461" s="23"/>
+      <x:c r="A461"/>
+      <x:c r="B461"/>
     </x:row>
     <x:row r="462">
-      <x:c r="A462" s="23"/>
-      <x:c r="B462" s="23"/>
+      <x:c r="A462"/>
+      <x:c r="B462"/>
     </x:row>
     <x:row r="463">
-      <x:c r="A463" s="23"/>
-      <x:c r="B463" s="23"/>
+      <x:c r="A463"/>
+      <x:c r="B463"/>
     </x:row>
     <x:row r="464">
-      <x:c r="A464" s="23"/>
-      <x:c r="B464" s="23"/>
+      <x:c r="A464"/>
+      <x:c r="B464"/>
     </x:row>
     <x:row r="465">
-      <x:c r="A465" s="23"/>
-      <x:c r="B465" s="23"/>
+      <x:c r="A465"/>
+      <x:c r="B465"/>
     </x:row>
     <x:row r="466">
-      <x:c r="A466" s="23"/>
-      <x:c r="B466" s="23"/>
+      <x:c r="A466"/>
+      <x:c r="B466"/>
     </x:row>
     <x:row r="467">
-      <x:c r="A467" s="23"/>
-      <x:c r="B467" s="23"/>
+      <x:c r="A467"/>
+      <x:c r="B467"/>
     </x:row>
     <x:row r="468">
-      <x:c r="A468" s="23"/>
-      <x:c r="B468" s="23"/>
+      <x:c r="A468"/>
+      <x:c r="B468"/>
     </x:row>
     <x:row r="469">
-      <x:c r="A469" s="23"/>
-      <x:c r="B469" s="23"/>
+      <x:c r="A469"/>
+      <x:c r="B469"/>
     </x:row>
     <x:row r="470">
-      <x:c r="A470" s="23"/>
-      <x:c r="B470" s="23"/>
+      <x:c r="A470"/>
+      <x:c r="B470"/>
     </x:row>
     <x:row r="471">
-      <x:c r="A471" s="23"/>
-      <x:c r="B471" s="23"/>
+      <x:c r="A471"/>
+      <x:c r="B471"/>
     </x:row>
     <x:row r="472">
-      <x:c r="A472" s="23"/>
-      <x:c r="B472" s="23"/>
+      <x:c r="A472"/>
+      <x:c r="B472"/>
     </x:row>
     <x:row r="473">
-      <x:c r="A473" s="23"/>
-      <x:c r="B473" s="23"/>
+      <x:c r="A473"/>
+      <x:c r="B473"/>
     </x:row>
     <x:row r="474">
-      <x:c r="A474" s="23"/>
-      <x:c r="B474" s="23"/>
+      <x:c r="A474"/>
+      <x:c r="B474"/>
     </x:row>
     <x:row r="475">
-      <x:c r="A475" s="23"/>
-      <x:c r="B475" s="23"/>
+      <x:c r="A475"/>
+      <x:c r="B475"/>
     </x:row>
     <x:row r="476">
-      <x:c r="A476" s="23"/>
-      <x:c r="B476" s="23"/>
+      <x:c r="A476"/>
+      <x:c r="B476"/>
     </x:row>
     <x:row r="477">
-      <x:c r="A477" s="23"/>
-      <x:c r="B477" s="23"/>
+      <x:c r="A477"/>
+      <x:c r="B477"/>
     </x:row>
     <x:row r="478">
-      <x:c r="A478" s="23"/>
-      <x:c r="B478" s="23"/>
+      <x:c r="A478"/>
+      <x:c r="B478"/>
     </x:row>
     <x:row r="479">
-      <x:c r="A479" s="23"/>
-      <x:c r="B479" s="23"/>
+      <x:c r="A479"/>
+      <x:c r="B479"/>
     </x:row>
     <x:row r="480">
-      <x:c r="A480" s="23"/>
-      <x:c r="B480" s="23"/>
+      <x:c r="A480"/>
+      <x:c r="B480"/>
     </x:row>
     <x:row r="481">
-      <x:c r="A481" s="23"/>
-      <x:c r="B481" s="23"/>
+      <x:c r="A481"/>
+      <x:c r="B481"/>
     </x:row>
     <x:row r="482">
-      <x:c r="A482" s="23"/>
-      <x:c r="B482" s="23"/>
+      <x:c r="A482"/>
+      <x:c r="B482"/>
     </x:row>
     <x:row r="483">
-      <x:c r="A483" s="23"/>
-      <x:c r="B483" s="23"/>
+      <x:c r="A483"/>
+      <x:c r="B483"/>
     </x:row>
     <x:row r="484">
-      <x:c r="A484" s="23"/>
-      <x:c r="B484" s="23"/>
+      <x:c r="A484"/>
+      <x:c r="B484"/>
     </x:row>
     <x:row r="485">
-      <x:c r="A485" s="23"/>
-      <x:c r="B485" s="23"/>
+      <x:c r="A485"/>
+      <x:c r="B485"/>
     </x:row>
     <x:row r="486">
-      <x:c r="A486" s="23"/>
-      <x:c r="B486" s="23"/>
+      <x:c r="A486"/>
+      <x:c r="B486"/>
     </x:row>
     <x:row r="487">
-      <x:c r="A487" s="23"/>
-      <x:c r="B487" s="23"/>
+      <x:c r="A487"/>
+      <x:c r="B487"/>
     </x:row>
     <x:row r="488">
-      <x:c r="A488" s="23"/>
-      <x:c r="B488" s="23"/>
+      <x:c r="A488"/>
+      <x:c r="B488"/>
     </x:row>
     <x:row r="489">
-      <x:c r="A489" s="23"/>
-      <x:c r="B489" s="23"/>
+      <x:c r="A489"/>
+      <x:c r="B489"/>
     </x:row>
     <x:row r="490">
-      <x:c r="A490" s="23"/>
-      <x:c r="B490" s="23"/>
+      <x:c r="A490"/>
+      <x:c r="B490"/>
     </x:row>
     <x:row r="491">
-      <x:c r="A491" s="23"/>
-      <x:c r="B491" s="23"/>
+      <x:c r="A491"/>
+      <x:c r="B491"/>
     </x:row>
     <x:row r="492">
-      <x:c r="A492" s="23"/>
-      <x:c r="B492" s="23"/>
+      <x:c r="A492"/>
+      <x:c r="B492"/>
     </x:row>
     <x:row r="493">
-      <x:c r="A493" s="23"/>
-      <x:c r="B493" s="23"/>
+      <x:c r="A493"/>
+      <x:c r="B493"/>
     </x:row>
     <x:row r="494">
-      <x:c r="A494" s="23"/>
-      <x:c r="B494" s="23"/>
+      <x:c r="A494"/>
+      <x:c r="B494"/>
     </x:row>
     <x:row r="495">
-      <x:c r="A495" s="23"/>
-      <x:c r="B495" s="23"/>
+      <x:c r="A495"/>
+      <x:c r="B495"/>
     </x:row>
     <x:row r="496">
-      <x:c r="A496" s="23"/>
-      <x:c r="B496" s="23"/>
+      <x:c r="A496"/>
+      <x:c r="B496"/>
     </x:row>
     <x:row r="497">
-      <x:c r="A497" s="23"/>
-      <x:c r="B497" s="23"/>
+      <x:c r="A497"/>
+      <x:c r="B497"/>
     </x:row>
     <x:row r="498">
-      <x:c r="A498" s="23"/>
-      <x:c r="B498" s="23"/>
+      <x:c r="A498"/>
+      <x:c r="B498"/>
     </x:row>
     <x:row r="499">
-      <x:c r="A499" s="23"/>
-      <x:c r="B499" s="23"/>
+      <x:c r="A499"/>
+      <x:c r="B499"/>
     </x:row>
     <x:row r="500">
-      <x:c r="A500" s="23"/>
-      <x:c r="B500" s="23"/>
+      <x:c r="A500"/>
+      <x:c r="B500"/>
     </x:row>
     <x:row r="501">
-      <x:c r="A501" s="23"/>
-      <x:c r="B501" s="23"/>
+      <x:c r="A501"/>
+      <x:c r="B501"/>
     </x:row>
     <x:row r="502">
-      <x:c r="A502" s="23"/>
-      <x:c r="B502" s="23"/>
+      <x:c r="A502"/>
+      <x:c r="B502"/>
     </x:row>
     <x:row r="503">
-      <x:c r="A503" s="23"/>
-      <x:c r="B503" s="23"/>
+      <x:c r="A503"/>
+      <x:c r="B503"/>
     </x:row>
     <x:row r="504">
-      <x:c r="A504" s="23"/>
-      <x:c r="B504" s="23"/>
+      <x:c r="A504"/>
+      <x:c r="B504"/>
     </x:row>
     <x:row r="505">
-      <x:c r="A505" s="23"/>
-      <x:c r="B505" s="23"/>
+      <x:c r="A505"/>
+      <x:c r="B505"/>
     </x:row>
     <x:row r="506">
-      <x:c r="A506" s="23"/>
-      <x:c r="B506" s="23"/>
+      <x:c r="A506"/>
+      <x:c r="B506"/>
     </x:row>
     <x:row r="507">
-      <x:c r="A507" s="23"/>
-      <x:c r="B507" s="23"/>
+      <x:c r="A507"/>
+      <x:c r="B507"/>
     </x:row>
     <x:row r="508">
-      <x:c r="A508" s="23"/>
-      <x:c r="B508" s="23"/>
+      <x:c r="A508"/>
+      <x:c r="B508"/>
     </x:row>
     <x:row r="509">
-      <x:c r="A509" s="23"/>
-      <x:c r="B509" s="23"/>
+      <x:c r="A509"/>
+      <x:c r="B509"/>
     </x:row>
     <x:row r="510">
-      <x:c r="A510" s="23"/>
-      <x:c r="B510" s="23"/>
+      <x:c r="A510"/>
+      <x:c r="B510"/>
     </x:row>
     <x:row r="511">
-      <x:c r="A511" s="23"/>
-      <x:c r="B511" s="23"/>
+      <x:c r="A511"/>
+      <x:c r="B511"/>
     </x:row>
     <x:row r="512">
-      <x:c r="A512" s="23"/>
-      <x:c r="B512" s="23"/>
+      <x:c r="A512"/>
+      <x:c r="B512"/>
     </x:row>
     <x:row r="513">
-      <x:c r="A513" s="23"/>
-      <x:c r="B513" s="23"/>
+      <x:c r="A513"/>
+      <x:c r="B513"/>
     </x:row>
     <x:row r="514">
-      <x:c r="A514" s="23"/>
-      <x:c r="B514" s="23"/>
+      <x:c r="A514"/>
+      <x:c r="B514"/>
     </x:row>
     <x:row r="515">
-      <x:c r="A515" s="23"/>
-      <x:c r="B515" s="23"/>
+      <x:c r="A515"/>
+      <x:c r="B515"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -51982,497 +51982,497 @@
       <x:c r="G436" s="52"/>
     </x:row>
     <x:row r="437">
-      <x:c r="A437" s="51"/>
-      <x:c r="B437" s="51"/>
-      <x:c r="C437" s="52"/>
-      <x:c r="D437" s="52"/>
-      <x:c r="E437" s="52"/>
-      <x:c r="F437" s="52"/>
-      <x:c r="G437" s="52"/>
+      <x:c r="A437"/>
+      <x:c r="B437"/>
+      <x:c r="C437"/>
+      <x:c r="D437"/>
+      <x:c r="E437"/>
+      <x:c r="F437"/>
+      <x:c r="G437"/>
     </x:row>
     <x:row r="438">
-      <x:c r="A438" s="51"/>
-      <x:c r="B438" s="51"/>
-      <x:c r="C438" s="52"/>
-      <x:c r="D438" s="52"/>
-      <x:c r="E438" s="52"/>
-      <x:c r="F438" s="52"/>
-      <x:c r="G438" s="52"/>
+      <x:c r="A438"/>
+      <x:c r="B438"/>
+      <x:c r="C438"/>
+      <x:c r="D438"/>
+      <x:c r="E438"/>
+      <x:c r="F438"/>
+      <x:c r="G438"/>
     </x:row>
     <x:row r="439">
-      <x:c r="A439" s="51"/>
-      <x:c r="B439" s="51"/>
-      <x:c r="C439" s="52"/>
-      <x:c r="D439" s="52"/>
-      <x:c r="E439" s="52"/>
-      <x:c r="F439" s="52"/>
-      <x:c r="G439" s="52"/>
+      <x:c r="A439"/>
+      <x:c r="B439"/>
+      <x:c r="C439"/>
+      <x:c r="D439"/>
+      <x:c r="E439"/>
+      <x:c r="F439"/>
+      <x:c r="G439"/>
     </x:row>
     <x:row r="440">
-      <x:c r="A440" s="51"/>
-      <x:c r="B440" s="51"/>
-      <x:c r="C440" s="52"/>
-      <x:c r="D440" s="52"/>
-      <x:c r="E440" s="52"/>
-      <x:c r="F440" s="52"/>
-      <x:c r="G440" s="52"/>
+      <x:c r="A440"/>
+      <x:c r="B440"/>
+      <x:c r="C440"/>
+      <x:c r="D440"/>
+      <x:c r="E440"/>
+      <x:c r="F440"/>
+      <x:c r="G440"/>
     </x:row>
     <x:row r="441">
-      <x:c r="A441" s="51"/>
-      <x:c r="B441" s="51"/>
-      <x:c r="C441" s="52"/>
-      <x:c r="D441" s="52"/>
-      <x:c r="E441" s="52"/>
-      <x:c r="F441" s="52"/>
-      <x:c r="G441" s="52"/>
+      <x:c r="A441"/>
+      <x:c r="B441"/>
+      <x:c r="C441"/>
+      <x:c r="D441"/>
+      <x:c r="E441"/>
+      <x:c r="F441"/>
+      <x:c r="G441"/>
     </x:row>
     <x:row r="442">
-      <x:c r="A442" s="51"/>
-      <x:c r="B442" s="51"/>
-      <x:c r="C442" s="52"/>
-      <x:c r="D442" s="52"/>
-      <x:c r="E442" s="52"/>
-      <x:c r="F442" s="52"/>
-      <x:c r="G442" s="52"/>
+      <x:c r="A442"/>
+      <x:c r="B442"/>
+      <x:c r="C442"/>
+      <x:c r="D442"/>
+      <x:c r="E442"/>
+      <x:c r="F442"/>
+      <x:c r="G442"/>
     </x:row>
     <x:row r="443">
-      <x:c r="A443" s="51"/>
-      <x:c r="B443" s="51"/>
-      <x:c r="C443" s="52"/>
-      <x:c r="D443" s="52"/>
-      <x:c r="E443" s="52"/>
-      <x:c r="F443" s="52"/>
-      <x:c r="G443" s="52"/>
+      <x:c r="A443"/>
+      <x:c r="B443"/>
+      <x:c r="C443"/>
+      <x:c r="D443"/>
+      <x:c r="E443"/>
+      <x:c r="F443"/>
+      <x:c r="G443"/>
     </x:row>
     <x:row r="444">
-      <x:c r="A444" s="51"/>
-      <x:c r="B444" s="51"/>
-      <x:c r="C444" s="52"/>
-      <x:c r="D444" s="52"/>
-      <x:c r="E444" s="52"/>
-      <x:c r="F444" s="52"/>
-      <x:c r="G444" s="52"/>
+      <x:c r="A444"/>
+      <x:c r="B444"/>
+      <x:c r="C444"/>
+      <x:c r="D444"/>
+      <x:c r="E444"/>
+      <x:c r="F444"/>
+      <x:c r="G444"/>
     </x:row>
     <x:row r="445">
-      <x:c r="A445" s="51"/>
-      <x:c r="B445" s="51"/>
-      <x:c r="C445" s="52"/>
-      <x:c r="D445" s="52"/>
-      <x:c r="E445" s="52"/>
-      <x:c r="F445" s="52"/>
-      <x:c r="G445" s="52"/>
+      <x:c r="A445"/>
+      <x:c r="B445"/>
+      <x:c r="C445"/>
+      <x:c r="D445"/>
+      <x:c r="E445"/>
+      <x:c r="F445"/>
+      <x:c r="G445"/>
     </x:row>
     <x:row r="446">
-      <x:c r="A446" s="51"/>
-      <x:c r="B446" s="51"/>
-      <x:c r="C446" s="52"/>
-      <x:c r="D446" s="52"/>
-      <x:c r="E446" s="52"/>
-      <x:c r="F446" s="52"/>
-      <x:c r="G446" s="52"/>
+      <x:c r="A446"/>
+      <x:c r="B446"/>
+      <x:c r="C446"/>
+      <x:c r="D446"/>
+      <x:c r="E446"/>
+      <x:c r="F446"/>
+      <x:c r="G446"/>
     </x:row>
     <x:row r="447">
-      <x:c r="A447" s="51"/>
-      <x:c r="B447" s="51"/>
-      <x:c r="C447" s="52"/>
-      <x:c r="D447" s="52"/>
-      <x:c r="E447" s="52"/>
-      <x:c r="F447" s="52"/>
-      <x:c r="G447" s="52"/>
+      <x:c r="A447"/>
+      <x:c r="B447"/>
+      <x:c r="C447"/>
+      <x:c r="D447"/>
+      <x:c r="E447"/>
+      <x:c r="F447"/>
+      <x:c r="G447"/>
     </x:row>
     <x:row r="448">
-      <x:c r="A448" s="51"/>
-      <x:c r="B448" s="51"/>
-      <x:c r="C448" s="52"/>
-      <x:c r="D448" s="52"/>
-      <x:c r="E448" s="52"/>
-      <x:c r="F448" s="52"/>
-      <x:c r="G448" s="52"/>
+      <x:c r="A448"/>
+      <x:c r="B448"/>
+      <x:c r="C448"/>
+      <x:c r="D448"/>
+      <x:c r="E448"/>
+      <x:c r="F448"/>
+      <x:c r="G448"/>
     </x:row>
     <x:row r="449">
-      <x:c r="A449" s="51"/>
-      <x:c r="B449" s="51"/>
-      <x:c r="C449" s="52"/>
-      <x:c r="D449" s="52"/>
-      <x:c r="E449" s="52"/>
-      <x:c r="F449" s="52"/>
-      <x:c r="G449" s="52"/>
+      <x:c r="A449"/>
+      <x:c r="B449"/>
+      <x:c r="C449"/>
+      <x:c r="D449"/>
+      <x:c r="E449"/>
+      <x:c r="F449"/>
+      <x:c r="G449"/>
     </x:row>
     <x:row r="450">
-      <x:c r="A450" s="51"/>
-      <x:c r="B450" s="51"/>
-      <x:c r="C450" s="52"/>
-      <x:c r="D450" s="52"/>
-      <x:c r="E450" s="52"/>
-      <x:c r="F450" s="52"/>
-      <x:c r="G450" s="52"/>
+      <x:c r="A450"/>
+      <x:c r="B450"/>
+      <x:c r="C450"/>
+      <x:c r="D450"/>
+      <x:c r="E450"/>
+      <x:c r="F450"/>
+      <x:c r="G450"/>
     </x:row>
     <x:row r="451">
-      <x:c r="A451" s="51"/>
-      <x:c r="B451" s="51"/>
-      <x:c r="C451" s="52"/>
-      <x:c r="D451" s="52"/>
-      <x:c r="E451" s="52"/>
-      <x:c r="F451" s="52"/>
-      <x:c r="G451" s="52"/>
+      <x:c r="A451"/>
+      <x:c r="B451"/>
+      <x:c r="C451"/>
+      <x:c r="D451"/>
+      <x:c r="E451"/>
+      <x:c r="F451"/>
+      <x:c r="G451"/>
     </x:row>
     <x:row r="452">
-      <x:c r="A452" s="51"/>
-      <x:c r="B452" s="51"/>
-      <x:c r="C452" s="52"/>
-      <x:c r="D452" s="52"/>
-      <x:c r="E452" s="52"/>
-      <x:c r="F452" s="52"/>
-      <x:c r="G452" s="52"/>
+      <x:c r="A452"/>
+      <x:c r="B452"/>
+      <x:c r="C452"/>
+      <x:c r="D452"/>
+      <x:c r="E452"/>
+      <x:c r="F452"/>
+      <x:c r="G452"/>
     </x:row>
     <x:row r="453">
-      <x:c r="A453" s="51"/>
-      <x:c r="B453" s="51"/>
-      <x:c r="C453" s="52"/>
-      <x:c r="D453" s="52"/>
-      <x:c r="E453" s="52"/>
-      <x:c r="F453" s="52"/>
-      <x:c r="G453" s="52"/>
+      <x:c r="A453"/>
+      <x:c r="B453"/>
+      <x:c r="C453"/>
+      <x:c r="D453"/>
+      <x:c r="E453"/>
+      <x:c r="F453"/>
+      <x:c r="G453"/>
     </x:row>
     <x:row r="454">
-      <x:c r="A454" s="51"/>
-      <x:c r="B454" s="51"/>
-      <x:c r="C454" s="52"/>
-      <x:c r="D454" s="52"/>
-      <x:c r="E454" s="52"/>
-      <x:c r="F454" s="52"/>
-      <x:c r="G454" s="52"/>
+      <x:c r="A454"/>
+      <x:c r="B454"/>
+      <x:c r="C454"/>
+      <x:c r="D454"/>
+      <x:c r="E454"/>
+      <x:c r="F454"/>
+      <x:c r="G454"/>
     </x:row>
     <x:row r="455">
-      <x:c r="A455" s="51"/>
-      <x:c r="B455" s="51"/>
-      <x:c r="C455" s="52"/>
-      <x:c r="D455" s="52"/>
-      <x:c r="E455" s="52"/>
-      <x:c r="F455" s="52"/>
-      <x:c r="G455" s="52"/>
+      <x:c r="A455"/>
+      <x:c r="B455"/>
+      <x:c r="C455"/>
+      <x:c r="D455"/>
+      <x:c r="E455"/>
+      <x:c r="F455"/>
+      <x:c r="G455"/>
     </x:row>
     <x:row r="456">
-      <x:c r="A456" s="51"/>
-      <x:c r="B456" s="51"/>
-      <x:c r="C456" s="52"/>
-      <x:c r="D456" s="52"/>
-      <x:c r="E456" s="52"/>
-      <x:c r="F456" s="52"/>
-      <x:c r="G456" s="52"/>
+      <x:c r="A456"/>
+      <x:c r="B456"/>
+      <x:c r="C456"/>
+      <x:c r="D456"/>
+      <x:c r="E456"/>
+      <x:c r="F456"/>
+      <x:c r="G456"/>
     </x:row>
     <x:row r="457">
-      <x:c r="A457" s="51"/>
-      <x:c r="B457" s="51"/>
-      <x:c r="C457" s="52"/>
-      <x:c r="D457" s="52"/>
-      <x:c r="E457" s="52"/>
-      <x:c r="F457" s="52"/>
-      <x:c r="G457" s="52"/>
+      <x:c r="A457"/>
+      <x:c r="B457"/>
+      <x:c r="C457"/>
+      <x:c r="D457"/>
+      <x:c r="E457"/>
+      <x:c r="F457"/>
+      <x:c r="G457"/>
     </x:row>
     <x:row r="458">
-      <x:c r="A458" s="51"/>
-      <x:c r="B458" s="51"/>
-      <x:c r="C458" s="52"/>
-      <x:c r="D458" s="52"/>
-      <x:c r="E458" s="52"/>
-      <x:c r="F458" s="52"/>
-      <x:c r="G458" s="52"/>
+      <x:c r="A458"/>
+      <x:c r="B458"/>
+      <x:c r="C458"/>
+      <x:c r="D458"/>
+      <x:c r="E458"/>
+      <x:c r="F458"/>
+      <x:c r="G458"/>
     </x:row>
     <x:row r="459">
-      <x:c r="A459" s="51"/>
-      <x:c r="B459" s="51"/>
-      <x:c r="C459" s="52"/>
-      <x:c r="D459" s="52"/>
-      <x:c r="E459" s="52"/>
-      <x:c r="F459" s="52"/>
-      <x:c r="G459" s="52"/>
+      <x:c r="A459"/>
+      <x:c r="B459"/>
+      <x:c r="C459"/>
+      <x:c r="D459"/>
+      <x:c r="E459"/>
+      <x:c r="F459"/>
+      <x:c r="G459"/>
     </x:row>
     <x:row r="460">
-      <x:c r="A460" s="51"/>
-      <x:c r="B460" s="51"/>
-      <x:c r="C460" s="52"/>
-      <x:c r="D460" s="52"/>
-      <x:c r="E460" s="52"/>
-      <x:c r="F460" s="52"/>
-      <x:c r="G460" s="52"/>
+      <x:c r="A460"/>
+      <x:c r="B460"/>
+      <x:c r="C460"/>
+      <x:c r="D460"/>
+      <x:c r="E460"/>
+      <x:c r="F460"/>
+      <x:c r="G460"/>
     </x:row>
     <x:row r="461">
-      <x:c r="A461" s="51"/>
-      <x:c r="B461" s="51"/>
-      <x:c r="C461" s="52"/>
-      <x:c r="D461" s="52"/>
-      <x:c r="E461" s="52"/>
-      <x:c r="F461" s="52"/>
-      <x:c r="G461" s="52"/>
+      <x:c r="A461"/>
+      <x:c r="B461"/>
+      <x:c r="C461"/>
+      <x:c r="D461"/>
+      <x:c r="E461"/>
+      <x:c r="F461"/>
+      <x:c r="G461"/>
     </x:row>
     <x:row r="462">
-      <x:c r="A462" s="51"/>
-      <x:c r="B462" s="51"/>
-      <x:c r="C462" s="52"/>
-      <x:c r="D462" s="52"/>
-      <x:c r="E462" s="52"/>
-      <x:c r="F462" s="52"/>
-      <x:c r="G462" s="52"/>
+      <x:c r="A462"/>
+      <x:c r="B462"/>
+      <x:c r="C462"/>
+      <x:c r="D462"/>
+      <x:c r="E462"/>
+      <x:c r="F462"/>
+      <x:c r="G462"/>
     </x:row>
     <x:row r="463">
-      <x:c r="A463" s="51"/>
-      <x:c r="B463" s="51"/>
-      <x:c r="C463" s="52"/>
-      <x:c r="D463" s="52"/>
-      <x:c r="E463" s="52"/>
-      <x:c r="F463" s="52"/>
-      <x:c r="G463" s="52"/>
+      <x:c r="A463"/>
+      <x:c r="B463"/>
+      <x:c r="C463"/>
+      <x:c r="D463"/>
+      <x:c r="E463"/>
+      <x:c r="F463"/>
+      <x:c r="G463"/>
     </x:row>
     <x:row r="464">
-      <x:c r="A464" s="51"/>
-      <x:c r="B464" s="51"/>
-      <x:c r="C464" s="52"/>
-      <x:c r="D464" s="52"/>
-      <x:c r="E464" s="52"/>
-      <x:c r="F464" s="52"/>
-      <x:c r="G464" s="52"/>
+      <x:c r="A464"/>
+      <x:c r="B464"/>
+      <x:c r="C464"/>
+      <x:c r="D464"/>
+      <x:c r="E464"/>
+      <x:c r="F464"/>
+      <x:c r="G464"/>
     </x:row>
     <x:row r="465">
-      <x:c r="A465" s="51"/>
-      <x:c r="B465" s="51"/>
-      <x:c r="C465" s="52"/>
-      <x:c r="D465" s="52"/>
-      <x:c r="E465" s="52"/>
-      <x:c r="F465" s="52"/>
-      <x:c r="G465" s="52"/>
+      <x:c r="A465"/>
+      <x:c r="B465"/>
+      <x:c r="C465"/>
+      <x:c r="D465"/>
+      <x:c r="E465"/>
+      <x:c r="F465"/>
+      <x:c r="G465"/>
     </x:row>
     <x:row r="466">
-      <x:c r="A466" s="23"/>
-      <x:c r="B466" s="23"/>
+      <x:c r="A466"/>
+      <x:c r="B466"/>
     </x:row>
     <x:row r="467">
-      <x:c r="A467" s="23"/>
-      <x:c r="B467" s="23"/>
+      <x:c r="A467"/>
+      <x:c r="B467"/>
     </x:row>
     <x:row r="468">
-      <x:c r="A468" s="23"/>
-      <x:c r="B468" s="23"/>
+      <x:c r="A468"/>
+      <x:c r="B468"/>
     </x:row>
     <x:row r="469">
-      <x:c r="A469" s="23"/>
-      <x:c r="B469" s="23"/>
+      <x:c r="A469"/>
+      <x:c r="B469"/>
     </x:row>
     <x:row r="470">
-      <x:c r="A470" s="23"/>
-      <x:c r="B470" s="23"/>
+      <x:c r="A470"/>
+      <x:c r="B470"/>
     </x:row>
     <x:row r="471">
-      <x:c r="A471" s="23"/>
-      <x:c r="B471" s="23"/>
+      <x:c r="A471"/>
+      <x:c r="B471"/>
     </x:row>
     <x:row r="472">
-      <x:c r="A472" s="23"/>
-      <x:c r="B472" s="23"/>
+      <x:c r="A472"/>
+      <x:c r="B472"/>
     </x:row>
     <x:row r="473">
-      <x:c r="A473" s="23"/>
-      <x:c r="B473" s="23"/>
+      <x:c r="A473"/>
+      <x:c r="B473"/>
     </x:row>
     <x:row r="474">
-      <x:c r="A474" s="23"/>
-      <x:c r="B474" s="23"/>
+      <x:c r="A474"/>
+      <x:c r="B474"/>
     </x:row>
     <x:row r="475">
-      <x:c r="A475" s="23"/>
-      <x:c r="B475" s="23"/>
+      <x:c r="A475"/>
+      <x:c r="B475"/>
     </x:row>
     <x:row r="476">
-      <x:c r="A476" s="23"/>
-      <x:c r="B476" s="23"/>
+      <x:c r="A476"/>
+      <x:c r="B476"/>
     </x:row>
     <x:row r="477">
-      <x:c r="A477" s="23"/>
-      <x:c r="B477" s="23"/>
+      <x:c r="A477"/>
+      <x:c r="B477"/>
     </x:row>
     <x:row r="478">
-      <x:c r="A478" s="23"/>
-      <x:c r="B478" s="23"/>
+      <x:c r="A478"/>
+      <x:c r="B478"/>
     </x:row>
     <x:row r="479">
-      <x:c r="A479" s="23"/>
-      <x:c r="B479" s="23"/>
+      <x:c r="A479"/>
+      <x:c r="B479"/>
     </x:row>
     <x:row r="480">
-      <x:c r="A480" s="23"/>
-      <x:c r="B480" s="23"/>
+      <x:c r="A480"/>
+      <x:c r="B480"/>
     </x:row>
     <x:row r="481">
-      <x:c r="A481" s="23"/>
-      <x:c r="B481" s="23"/>
+      <x:c r="A481"/>
+      <x:c r="B481"/>
     </x:row>
     <x:row r="482">
-      <x:c r="A482" s="23"/>
-      <x:c r="B482" s="23"/>
+      <x:c r="A482"/>
+      <x:c r="B482"/>
     </x:row>
     <x:row r="483">
-      <x:c r="A483" s="23"/>
-      <x:c r="B483" s="23"/>
+      <x:c r="A483"/>
+      <x:c r="B483"/>
     </x:row>
     <x:row r="484">
-      <x:c r="A484" s="23"/>
-      <x:c r="B484" s="23"/>
+      <x:c r="A484"/>
+      <x:c r="B484"/>
     </x:row>
     <x:row r="485">
-      <x:c r="A485" s="23"/>
-      <x:c r="B485" s="23"/>
+      <x:c r="A485"/>
+      <x:c r="B485"/>
     </x:row>
     <x:row r="486">
-      <x:c r="A486" s="23"/>
-      <x:c r="B486" s="23"/>
+      <x:c r="A486"/>
+      <x:c r="B486"/>
     </x:row>
     <x:row r="487">
-      <x:c r="A487" s="23"/>
-      <x:c r="B487" s="23"/>
+      <x:c r="A487"/>
+      <x:c r="B487"/>
     </x:row>
     <x:row r="488">
-      <x:c r="A488" s="23"/>
-      <x:c r="B488" s="23"/>
+      <x:c r="A488"/>
+      <x:c r="B488"/>
     </x:row>
     <x:row r="489">
-      <x:c r="A489" s="23"/>
-      <x:c r="B489" s="23"/>
+      <x:c r="A489"/>
+      <x:c r="B489"/>
     </x:row>
     <x:row r="490">
-      <x:c r="A490" s="23"/>
-      <x:c r="B490" s="23"/>
+      <x:c r="A490"/>
+      <x:c r="B490"/>
     </x:row>
     <x:row r="491">
-      <x:c r="A491" s="23"/>
-      <x:c r="B491" s="23"/>
+      <x:c r="A491"/>
+      <x:c r="B491"/>
     </x:row>
     <x:row r="492">
-      <x:c r="A492" s="23"/>
-      <x:c r="B492" s="23"/>
+      <x:c r="A492"/>
+      <x:c r="B492"/>
     </x:row>
     <x:row r="493">
-      <x:c r="A493" s="23"/>
-      <x:c r="B493" s="23"/>
+      <x:c r="A493"/>
+      <x:c r="B493"/>
     </x:row>
     <x:row r="494">
-      <x:c r="A494" s="23"/>
-      <x:c r="B494" s="23"/>
+      <x:c r="A494"/>
+      <x:c r="B494"/>
     </x:row>
     <x:row r="495">
-      <x:c r="A495" s="23"/>
-      <x:c r="B495" s="23"/>
+      <x:c r="A495"/>
+      <x:c r="B495"/>
     </x:row>
     <x:row r="496">
-      <x:c r="A496" s="23"/>
-      <x:c r="B496" s="23"/>
+      <x:c r="A496"/>
+      <x:c r="B496"/>
     </x:row>
     <x:row r="497">
-      <x:c r="A497" s="23"/>
-      <x:c r="B497" s="23"/>
+      <x:c r="A497"/>
+      <x:c r="B497"/>
     </x:row>
     <x:row r="498">
-      <x:c r="A498" s="23"/>
-      <x:c r="B498" s="23"/>
+      <x:c r="A498"/>
+      <x:c r="B498"/>
     </x:row>
     <x:row r="499">
-      <x:c r="A499" s="23"/>
-      <x:c r="B499" s="23"/>
+      <x:c r="A499"/>
+      <x:c r="B499"/>
     </x:row>
     <x:row r="500">
-      <x:c r="A500" s="23"/>
-      <x:c r="B500" s="23"/>
+      <x:c r="A500"/>
+      <x:c r="B500"/>
     </x:row>
     <x:row r="501">
-      <x:c r="A501" s="23"/>
-      <x:c r="B501" s="23"/>
+      <x:c r="A501"/>
+      <x:c r="B501"/>
     </x:row>
     <x:row r="502">
-      <x:c r="A502" s="23"/>
-      <x:c r="B502" s="23"/>
+      <x:c r="A502"/>
+      <x:c r="B502"/>
     </x:row>
     <x:row r="503">
-      <x:c r="A503" s="23"/>
-      <x:c r="B503" s="23"/>
+      <x:c r="A503"/>
+      <x:c r="B503"/>
     </x:row>
     <x:row r="504">
-      <x:c r="A504" s="23"/>
-      <x:c r="B504" s="23"/>
+      <x:c r="A504"/>
+      <x:c r="B504"/>
     </x:row>
     <x:row r="505">
-      <x:c r="A505" s="23"/>
-      <x:c r="B505" s="23"/>
+      <x:c r="A505"/>
+      <x:c r="B505"/>
     </x:row>
     <x:row r="506">
-      <x:c r="A506" s="23"/>
-      <x:c r="B506" s="23"/>
+      <x:c r="A506"/>
+      <x:c r="B506"/>
     </x:row>
     <x:row r="507">
-      <x:c r="A507" s="23"/>
-      <x:c r="B507" s="23"/>
+      <x:c r="A507"/>
+      <x:c r="B507"/>
     </x:row>
     <x:row r="508">
-      <x:c r="A508" s="23"/>
-      <x:c r="B508" s="23"/>
+      <x:c r="A508"/>
+      <x:c r="B508"/>
     </x:row>
     <x:row r="509">
-      <x:c r="A509" s="23"/>
-      <x:c r="B509" s="23"/>
+      <x:c r="A509"/>
+      <x:c r="B509"/>
     </x:row>
     <x:row r="510">
-      <x:c r="A510" s="23"/>
-      <x:c r="B510" s="23"/>
+      <x:c r="A510"/>
+      <x:c r="B510"/>
     </x:row>
     <x:row r="511">
-      <x:c r="A511" s="23"/>
-      <x:c r="B511" s="23"/>
+      <x:c r="A511"/>
+      <x:c r="B511"/>
     </x:row>
     <x:row r="512">
-      <x:c r="A512" s="23"/>
-      <x:c r="B512" s="23"/>
+      <x:c r="A512"/>
+      <x:c r="B512"/>
     </x:row>
     <x:row r="513">
-      <x:c r="A513" s="23"/>
-      <x:c r="B513" s="23"/>
+      <x:c r="A513"/>
+      <x:c r="B513"/>
     </x:row>
     <x:row r="514">
-      <x:c r="A514" s="23"/>
-      <x:c r="B514" s="23"/>
+      <x:c r="A514"/>
+      <x:c r="B514"/>
     </x:row>
     <x:row r="515">
-      <x:c r="A515" s="23"/>
-      <x:c r="B515" s="23"/>
+      <x:c r="A515"/>
+      <x:c r="B515"/>
     </x:row>
     <x:row r="516">
-      <x:c r="A516" s="23"/>
-      <x:c r="B516" s="23"/>
+      <x:c r="A516"/>
+      <x:c r="B516"/>
     </x:row>
     <x:row r="517">
-      <x:c r="A517" s="23"/>
-      <x:c r="B517" s="23"/>
+      <x:c r="A517"/>
+      <x:c r="B517"/>
     </x:row>
     <x:row r="518">
-      <x:c r="A518" s="23"/>
-      <x:c r="B518" s="23"/>
+      <x:c r="A518"/>
+      <x:c r="B518"/>
     </x:row>
     <x:row r="519">
-      <x:c r="A519" s="23"/>
-      <x:c r="B519" s="23"/>
+      <x:c r="A519"/>
+      <x:c r="B519"/>
     </x:row>
     <x:row r="520">
-      <x:c r="A520" s="23"/>
-      <x:c r="B520" s="23"/>
+      <x:c r="A520"/>
+      <x:c r="B520"/>
     </x:row>
     <x:row r="521">
-      <x:c r="A521" s="23"/>
-      <x:c r="B521" s="23"/>
+      <x:c r="A521"/>
+      <x:c r="B521"/>
     </x:row>
     <x:row r="522">
-      <x:c r="A522" s="23"/>
-      <x:c r="B522" s="23"/>
+      <x:c r="A522"/>
+      <x:c r="B522"/>
     </x:row>
     <x:row r="523">
-      <x:c r="A523" s="23"/>
-      <x:c r="B523" s="23"/>
+      <x:c r="A523"/>
+      <x:c r="B523"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -53010,7 +53010,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B12" t="str">
-        <x:v>PD Guide Toolkit v5.2.5 adds Labor Mapping with independent Province/Postal Code search.</x:v>
+        <x:v>PD Guide Toolkit v5.2.6 adds selective inline Related Guide ⓘ popups in SYMPTOMS.</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
